--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,35 +487,35 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11028</v>
+        <v>7258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10970</v>
+        <v>7183</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-11 13:00</t>
+          <t>2026-09-11 15:00</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>11045</v>
+        <v>7274</v>
       </c>
       <c r="H2" t="n">
-        <v>11045</v>
+        <v>7274</v>
       </c>
       <c r="I2" t="n">
-        <v>10922</v>
+        <v>7174.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,35 +524,35 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>235.84</v>
+        <v>11028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-08 11:45</t>
+          <t>2026-09-08 09:15</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>235.39</v>
+        <v>10970</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-11 10:00</t>
+          <t>2026-09-11 13:00</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>236.49</v>
+        <v>11045</v>
       </c>
       <c r="H3" t="n">
-        <v>236.49</v>
+        <v>11045</v>
       </c>
       <c r="I3" t="n">
-        <v>234.06</v>
+        <v>10922</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,35 +561,35 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>402.9</v>
+        <v>235.84</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-10 09:15</t>
+          <t>2026-09-08 11:45</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>402.8</v>
+        <v>235.39</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-11 11:00</t>
+          <t>2026-09-11 10:00</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>403.05</v>
+        <v>236.49</v>
       </c>
       <c r="H4" t="n">
-        <v>403.05</v>
+        <v>236.49</v>
       </c>
       <c r="I4" t="n">
-        <v>399.75</v>
+        <v>234.06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -598,35 +598,35 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1151</v>
+        <v>402.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-10 09:15</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1144.3</v>
+        <v>402.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-11 10:45</t>
+          <t>2026-09-11 11:00</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1156.2</v>
+        <v>403.05</v>
       </c>
       <c r="H5" t="n">
-        <v>1156.2</v>
+        <v>403.05</v>
       </c>
       <c r="I5" t="n">
-        <v>1132</v>
+        <v>399.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>859.55</v>
+        <v>1151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -643,27 +643,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>858.05</v>
+        <v>1144.3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-11 10:45</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>860.65</v>
+        <v>1156.2</v>
       </c>
       <c r="H6" t="n">
-        <v>860.65</v>
+        <v>1156.2</v>
       </c>
       <c r="I6" t="n">
-        <v>855.45</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -672,35 +672,35 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>698.5</v>
+        <v>859.55</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15</t>
+          <t>2026-09-08 09:15</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>696.5</v>
+        <v>858.05</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-11 13:45</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>701.65</v>
+        <v>860.65</v>
       </c>
       <c r="H7" t="n">
-        <v>701.65</v>
+        <v>860.65</v>
       </c>
       <c r="I7" t="n">
-        <v>682.1</v>
+        <v>855.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -709,15 +709,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4908.5</v>
+        <v>698.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-10 09:30</t>
+          <t>2026-09-09 09:15</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4900</v>
+        <v>696.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4926</v>
+        <v>701.65</v>
       </c>
       <c r="H8" t="n">
-        <v>4926</v>
+        <v>701.65</v>
       </c>
       <c r="I8" t="n">
-        <v>4822</v>
+        <v>682.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -746,35 +746,35 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>134.32</v>
+        <v>4908.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-08 12:15</t>
+          <t>2026-09-10 09:30</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>134.25</v>
+        <v>4900</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-11 12:15</t>
+          <t>2026-09-11 13:45</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>134.4</v>
+        <v>4926</v>
       </c>
       <c r="H9" t="n">
-        <v>134.4</v>
+        <v>4926</v>
       </c>
       <c r="I9" t="n">
-        <v>133.11</v>
+        <v>4822</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -783,35 +783,35 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>418.95</v>
+        <v>134.32</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15</t>
+          <t>2026-09-08 12:15</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>418</v>
+        <v>134.25</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00</t>
+          <t>2026-09-11 12:15</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>419</v>
+        <v>134.4</v>
       </c>
       <c r="H10" t="n">
-        <v>419</v>
+        <v>134.4</v>
       </c>
       <c r="I10" t="n">
-        <v>409.25</v>
+        <v>133.11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -820,35 +820,35 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1026.1</v>
+        <v>418.95</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-09 09:15</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1021</v>
+        <v>418</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-11 13:45</t>
+          <t>2026-09-11 15:00</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1028.3</v>
+        <v>419</v>
       </c>
       <c r="H11" t="n">
-        <v>1028.3</v>
+        <v>419</v>
       </c>
       <c r="I11" t="n">
-        <v>1013.3</v>
+        <v>409.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -857,65 +857,102 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>181.4</v>
+        <v>1026.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-08 09:15</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>180.86</v>
+        <v>1021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-11 13:45</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>182.28</v>
+        <v>1028.3</v>
       </c>
       <c r="H12" t="n">
-        <v>182.28</v>
+        <v>1028.3</v>
       </c>
       <c r="I12" t="n">
-        <v>180.86</v>
+        <v>1013.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>180.86</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>182.28</v>
+      </c>
+      <c r="H13" t="n">
+        <v>182.28</v>
+      </c>
+      <c r="I13" t="n">
+        <v>180.86</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>4952</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2026-09-11 09:15</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E14" t="n">
         <v>4945</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-09-11 09:45</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="G14" t="n">
         <v>4956</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H14" t="n">
         <v>4956</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>4945</v>
       </c>
     </row>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,482 +478,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7258</v>
+        <v>328.65</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-15 09:30</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7183</v>
+        <v>328</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00</t>
+          <t>2026-09-15 15:15</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7274</v>
+        <v>329.5</v>
       </c>
       <c r="H2" t="n">
-        <v>7274</v>
+        <v>329.5</v>
       </c>
       <c r="I2" t="n">
-        <v>7174.5</v>
+        <v>326.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11028</v>
+        <v>1834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-15 09:45</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10970</v>
+        <v>1829.9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-11 13:00</t>
+          <t>2026-09-15 12:00</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11045</v>
+        <v>1839.8</v>
       </c>
       <c r="H3" t="n">
-        <v>11045</v>
+        <v>1839.8</v>
       </c>
       <c r="I3" t="n">
-        <v>10922</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>235.84</v>
+        <v>256.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-08 11:45</t>
+          <t>2026-09-15 13:30</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>235.39</v>
+        <v>256</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-11 10:00</t>
+          <t>2026-09-15 15:15</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>236.49</v>
+        <v>257</v>
       </c>
       <c r="H4" t="n">
-        <v>236.49</v>
+        <v>257</v>
       </c>
       <c r="I4" t="n">
-        <v>234.06</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>402.9</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-09-10 09:15</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>402.8</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-09-11 11:00</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>403.05</v>
-      </c>
-      <c r="H5" t="n">
-        <v>403.05</v>
-      </c>
-      <c r="I5" t="n">
-        <v>399.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DRREDDY</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1151</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-09-08 09:15</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1144.3</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-11 10:45</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1156.2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1156.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GODREJCP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>859.55</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-09-08 09:15</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>858.05</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>860.65</v>
-      </c>
-      <c r="H7" t="n">
-        <v>860.65</v>
-      </c>
-      <c r="I7" t="n">
-        <v>855.45</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HDFCBANK</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>698.5</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-09-09 09:15</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>696.5</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:45</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>701.65</v>
-      </c>
-      <c r="H8" t="n">
-        <v>701.65</v>
-      </c>
-      <c r="I8" t="n">
-        <v>682.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>INDIGO</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>4908.5</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-10 09:30</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4900</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:45</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>4926</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4926</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4822</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>134.32</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-09-08 12:15</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>134.25</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-11 12:15</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>134.4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>134.4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>133.11</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>418.95</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-09-09 09:15</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>418</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-11 15:00</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>419</v>
-      </c>
-      <c r="H11" t="n">
-        <v>419</v>
-      </c>
-      <c r="I11" t="n">
-        <v>409.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1026.1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-09-08 09:15</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1021</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:45</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1028.3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1028.3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1013.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>181.4</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>180.86</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>182.28</v>
-      </c>
-      <c r="H13" t="n">
-        <v>182.28</v>
-      </c>
-      <c r="I13" t="n">
-        <v>180.86</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>4952</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>4945</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:45</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>4956</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4956</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4945</v>
+        <v>253.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,112 +478,778 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>328.65</v>
+        <v>2918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-15 09:30</t>
+          <t>2026-09-16 09:45</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>328</v>
+        <v>2915.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-15 15:15</t>
+          <t>2026-09-16 10:00</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>329.5</v>
+        <v>2925.1</v>
       </c>
       <c r="H2" t="n">
-        <v>329.5</v>
+        <v>2925.1</v>
       </c>
       <c r="I2" t="n">
-        <v>326.5</v>
+        <v>2915.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1834</v>
+        <v>1229.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-15 09:45</t>
+          <t>2026-09-15 13:30</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1829.9</v>
+        <v>1228.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-15 12:00</t>
+          <t>2026-09-16 09:45</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1839.8</v>
+        <v>1234</v>
       </c>
       <c r="H3" t="n">
-        <v>1839.8</v>
+        <v>1234</v>
       </c>
       <c r="I3" t="n">
-        <v>1828</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>256.5</v>
+        <v>11529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-15 10:30</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>11525</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:00</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>11593</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11593</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11381</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>234.05</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>2026-09-15 13:30</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>256</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-09-15 15:15</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>257</v>
-      </c>
-      <c r="H4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I4" t="n">
-        <v>253.6</v>
+      <c r="E5" t="n">
+        <v>233.95</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:00</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>234.98</v>
+      </c>
+      <c r="H5" t="n">
+        <v>234.98</v>
+      </c>
+      <c r="I5" t="n">
+        <v>232.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>122.65</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:00</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>122.46</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:15</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>122.97</v>
+      </c>
+      <c r="H6" t="n">
+        <v>122.97</v>
+      </c>
+      <c r="I6" t="n">
+        <v>121.84</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1347.7</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:30</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1346.8</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:45</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1348.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1348.6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9119.5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:15</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>9061.5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:00</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>9148.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9148.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8923</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>708.6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:30</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>707.7</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:00</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>709.75</v>
+      </c>
+      <c r="H9" t="n">
+        <v>709.75</v>
+      </c>
+      <c r="I9" t="n">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>133.02</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:00</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>133.01</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:45</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>133.55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>133.55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>131.72</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1075.5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:45</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1075.3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:00</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1079.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1079.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1048.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3069.1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:15</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3058.1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:30</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>3075.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3075.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3029.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1373.5</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:30</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1368.3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:15</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1384</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1384</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1540.4</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:30</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1540</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:30</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1543.4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1543.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1521.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>311.25</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:45</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>311</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:45</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>314.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>314.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>308.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:45</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1667.5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:45</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1672.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1672.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>180.79</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:00</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>180.29</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:00</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>180.91</v>
+      </c>
+      <c r="H17" t="n">
+        <v>180.91</v>
+      </c>
+      <c r="I17" t="n">
+        <v>180.29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2185.5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:30</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2179.1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:15</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2188.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2188.8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2172.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2757.5</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:15</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2756</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:45</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2772</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2772</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2727.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>175.53</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:00</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>175.22</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:45</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>176.26</v>
+      </c>
+      <c r="H20" t="n">
+        <v>176.26</v>
+      </c>
+      <c r="I20" t="n">
+        <v>174.81</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1384.3</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:00</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1383.7</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:15</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1388</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1388</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1368.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1104.6</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:15</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1103.8</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:30</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1106.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1106.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1086</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,44 +478,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2918</v>
+        <v>1230.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45</t>
+          <t>2026-09-15 11:00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2915.5</v>
+        <v>1225.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00</t>
+          <t>2026-09-17 15:00</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2925.1</v>
+        <v>1233.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2925.1</v>
+        <v>1233.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2915.5</v>
+        <v>1219.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,731 +524,1027 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1229.8</v>
+        <v>1364.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-15 13:30</t>
+          <t>2026-09-15 09:15</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1228.8</v>
+        <v>1359.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45</t>
+          <t>2026-09-16 11:30</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1234</v>
+        <v>1364.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1234</v>
+        <v>1364.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1220</v>
+        <v>1339.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11529</v>
+        <v>2918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-15 10:30</t>
+          <t>2026-09-16 09:45</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11525</v>
+        <v>2915.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00</t>
+          <t>2026-09-17 11:30</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11593</v>
+        <v>2928</v>
       </c>
       <c r="H4" t="n">
-        <v>11593</v>
+        <v>2928</v>
       </c>
       <c r="I4" t="n">
-        <v>11381</v>
+        <v>2907.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>234.05</v>
+        <v>1273.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-15 13:30</t>
+          <t>2026-09-15 10:45</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>233.95</v>
+        <v>1272.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00</t>
+          <t>2026-09-17 15:15</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>234.98</v>
+        <v>1274.2</v>
       </c>
       <c r="H5" t="n">
-        <v>234.98</v>
+        <v>1274.2</v>
       </c>
       <c r="I5" t="n">
-        <v>232.5</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>122.65</v>
+        <v>204.12</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-15 14:00</t>
+          <t>2026-09-15 12:00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>122.46</v>
+        <v>204.09</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-16 10:15</t>
+          <t>2026-09-17 13:30</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>122.97</v>
+        <v>204.51</v>
       </c>
       <c r="H6" t="n">
-        <v>122.97</v>
+        <v>204.51</v>
       </c>
       <c r="I6" t="n">
-        <v>121.84</v>
+        <v>200.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1347.7</v>
+        <v>8745</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-16 09:30</t>
+          <t>2026-09-15 15:15</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1346.8</v>
+        <v>8714</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45</t>
+          <t>2026-09-17 14:15</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1348.6</v>
+        <v>8753.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1348.6</v>
+        <v>8753.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1345</v>
+        <v>8675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9119.5</v>
+        <v>2442.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:15</t>
+          <t>2026-09-15 10:00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9061.5</v>
+        <v>2440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00</t>
+          <t>2026-09-17 14:00</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9148.5</v>
+        <v>2445.6</v>
       </c>
       <c r="H8" t="n">
-        <v>9148.5</v>
+        <v>2445.6</v>
       </c>
       <c r="I8" t="n">
-        <v>8923</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>708.6</v>
+        <v>10922</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-16 09:30</t>
+          <t>2026-09-17 09:15</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>707.7</v>
+        <v>10909</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00</t>
+          <t>2026-09-17 09:15</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>709.75</v>
+        <v>10994</v>
       </c>
       <c r="H9" t="n">
-        <v>709.75</v>
+        <v>10994</v>
       </c>
       <c r="I9" t="n">
-        <v>707</v>
+        <v>10909</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>133.02</v>
+        <v>418.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-15 14:00</t>
+          <t>2026-09-15 14:15</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>133.01</v>
+        <v>417.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-16 10:45</t>
+          <t>2026-09-17 11:15</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>133.55</v>
+        <v>419.45</v>
       </c>
       <c r="H10" t="n">
-        <v>133.55</v>
+        <v>419.45</v>
       </c>
       <c r="I10" t="n">
-        <v>131.72</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1075.5</v>
+        <v>122.65</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-15 13:45</t>
+          <t>2026-09-15 14:00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1075.3</v>
+        <v>122.46</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-16 12:00</t>
+          <t>2026-09-17 11:30</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1079.2</v>
+        <v>122.91</v>
       </c>
       <c r="H11" t="n">
-        <v>1079.2</v>
+        <v>122.91</v>
       </c>
       <c r="I11" t="n">
-        <v>1048.8</v>
+        <v>121.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3069.1</v>
+        <v>4965</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-15 14:15</t>
+          <t>2026-09-15 10:15</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3058.1</v>
+        <v>4956</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-16 14:30</t>
+          <t>2026-09-17 10:15</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3075.8</v>
+        <v>4966.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3075.8</v>
+        <v>4966.5</v>
       </c>
       <c r="I12" t="n">
-        <v>3029.5</v>
+        <v>4845</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1373.5</v>
+        <v>630</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-15 10:30</t>
+          <t>2026-09-15 10:45</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1368.3</v>
+        <v>628.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-16 09:15</t>
+          <t>2026-09-17 10:00</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1384</v>
+        <v>631.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1384</v>
+        <v>631.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1362</v>
+        <v>611.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1540.4</v>
+        <v>973.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-15 12:30</t>
+          <t>2026-09-15 09:15</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1540</v>
+        <v>966.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-16 13:30</t>
+          <t>2026-09-17 09:15</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1543.4</v>
+        <v>979.6</v>
       </c>
       <c r="H14" t="n">
-        <v>1543.4</v>
+        <v>979.6</v>
       </c>
       <c r="I14" t="n">
-        <v>1521.1</v>
+        <v>958.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>311.25</v>
+        <v>1443.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-15 14:45</t>
+          <t>2026-09-15 10:45</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>311</v>
+        <v>1443</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-16 10:45</t>
+          <t>2026-09-17 09:15</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>314.1</v>
+        <v>1447</v>
       </c>
       <c r="H15" t="n">
-        <v>314.1</v>
+        <v>1447</v>
       </c>
       <c r="I15" t="n">
-        <v>308.5</v>
+        <v>1423.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1671</v>
+        <v>4822</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-15 09:45</t>
+          <t>2026-09-15 14:15</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1667.5</v>
+        <v>4784</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-16 10:45</t>
+          <t>2026-09-17 11:45</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1672.7</v>
+        <v>4835.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1672.7</v>
+        <v>4835.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1653</v>
+        <v>4704.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>180.79</v>
+        <v>226.44</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00</t>
+          <t>2026-09-15 15:00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>180.29</v>
+        <v>226.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00</t>
+          <t>2026-09-17 09:15</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>180.91</v>
+        <v>226.98</v>
       </c>
       <c r="H17" t="n">
-        <v>180.91</v>
+        <v>226.98</v>
       </c>
       <c r="I17" t="n">
-        <v>180.29</v>
+        <v>224.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2185.5</v>
+        <v>3069.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-16 14:30</t>
+          <t>2026-09-15 14:15</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2179.1</v>
+        <v>3058.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-16 15:15</t>
+          <t>2026-09-17 09:15</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2188.8</v>
+        <v>3102.1</v>
       </c>
       <c r="H18" t="n">
-        <v>2188.8</v>
+        <v>3102.1</v>
       </c>
       <c r="I18" t="n">
-        <v>2172.6</v>
+        <v>3029.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2757.5</v>
+        <v>160.12</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-15 14:15</t>
+          <t>2026-09-15 14:00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2756</v>
+        <v>160</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-16 10:45</t>
+          <t>2026-09-17 09:15</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2772</v>
+        <v>161.35</v>
       </c>
       <c r="H19" t="n">
-        <v>2772</v>
+        <v>161.35</v>
       </c>
       <c r="I19" t="n">
-        <v>2727.8</v>
+        <v>156.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>175.53</v>
+        <v>328.65</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-15 14:00</t>
+          <t>2026-09-15 09:30</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>175.22</v>
+        <v>328</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45</t>
+          <t>2026-09-17 15:15</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>176.26</v>
+        <v>329.6</v>
       </c>
       <c r="H20" t="n">
-        <v>176.26</v>
+        <v>329.6</v>
       </c>
       <c r="I20" t="n">
-        <v>174.81</v>
+        <v>326.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1384.3</v>
+        <v>232.22</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-15 11:00</t>
+          <t>2026-09-17 13:15</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1383.7</v>
+        <v>232.15</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-16 10:15</t>
+          <t>2026-09-17 15:00</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1388</v>
+        <v>232.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1388</v>
+        <v>232.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1368.7</v>
+        <v>231.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1540.4</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:30</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1540</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:00</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1544</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1544</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1521.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>362.25</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:30</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>361.55</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-17 11:15</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>362.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>362.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>360.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2185.5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:30</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2179.1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:00</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>2188.9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2188.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2163.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4823</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:30</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4798</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:15</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>4838.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4838.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4756</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4062.8</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:15</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4054.6</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:15</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>4123.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4123.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4002.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1384.3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:00</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1383.7</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:00</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1390</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1390</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1368.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>256.5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:30</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>256</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:45</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>256.65</v>
+      </c>
+      <c r="H28" t="n">
+        <v>256.65</v>
+      </c>
+      <c r="I28" t="n">
+        <v>252.55</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>165.16</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:15</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>165.15</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:15</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>165.73</v>
+      </c>
+      <c r="H29" t="n">
+        <v>165.73</v>
+      </c>
+      <c r="I29" t="n">
+        <v>165.15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>1104.6</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2026-09-15 14:15</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E30" t="n">
         <v>1103.8</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-16 12:30</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>1106.7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1106.7</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:15</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1110.6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1110.6</v>
+      </c>
+      <c r="I30" t="n">
         <v>1086</v>
       </c>
     </row>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,127 +478,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1230.6</v>
+        <v>7173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:00</t>
+          <t>2026-09-15 09:15</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1225.3</v>
+        <v>7132.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-17 15:00</t>
+          <t>2026-09-18 13:45</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1233.6</v>
+        <v>7206</v>
       </c>
       <c r="H2" t="n">
-        <v>1233.6</v>
+        <v>7206</v>
       </c>
       <c r="I2" t="n">
-        <v>1219.3</v>
+        <v>6905.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1364.2</v>
+        <v>387.65</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-15 09:15</t>
+          <t>2026-09-15 10:45</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1359.6</v>
+        <v>387.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-16 11:30</t>
+          <t>2026-09-18 10:30</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1364.5</v>
+        <v>388.65</v>
       </c>
       <c r="H3" t="n">
-        <v>1364.5</v>
+        <v>388.65</v>
       </c>
       <c r="I3" t="n">
-        <v>1339.1</v>
+        <v>379.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2918</v>
+        <v>2442.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45</t>
+          <t>2026-09-15 10:00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2915.5</v>
+        <v>2440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-17 11:30</t>
+          <t>2026-09-18 13:00</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2928</v>
+        <v>2444.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2928</v>
+        <v>2444.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2907.8</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1273.2</v>
+        <v>592.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -606,332 +606,332 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1272.7</v>
+        <v>590.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-17 15:15</t>
+          <t>2026-09-18 09:15</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1274.2</v>
+        <v>614</v>
       </c>
       <c r="H5" t="n">
-        <v>1274.2</v>
+        <v>614</v>
       </c>
       <c r="I5" t="n">
-        <v>1247.5</v>
+        <v>578.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>204.12</v>
+        <v>234.05</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-15 12:00</t>
+          <t>2026-09-15 13:30</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>204.09</v>
+        <v>233.95</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30</t>
+          <t>2026-09-18 15:15</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>204.51</v>
+        <v>234.94</v>
       </c>
       <c r="H6" t="n">
-        <v>204.51</v>
+        <v>234.94</v>
       </c>
       <c r="I6" t="n">
-        <v>200.55</v>
+        <v>232.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8745</v>
+        <v>889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-15 15:15</t>
+          <t>2026-09-15 09:45</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8714</v>
+        <v>879</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-17 14:15</t>
+          <t>2026-09-18 09:15</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8753.5</v>
+        <v>891.35</v>
       </c>
       <c r="H7" t="n">
-        <v>8753.5</v>
+        <v>891.35</v>
       </c>
       <c r="I7" t="n">
-        <v>8675</v>
+        <v>839.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2442.8</v>
+        <v>1795.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-15 10:00</t>
+          <t>2026-09-15 11:15</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2440</v>
+        <v>1785.3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-17 14:00</t>
+          <t>2026-09-18 14:15</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2445.6</v>
+        <v>1798</v>
       </c>
       <c r="H8" t="n">
-        <v>2445.6</v>
+        <v>1798</v>
       </c>
       <c r="I8" t="n">
-        <v>2398</v>
+        <v>1748.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10922</v>
+        <v>172.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-17 09:15</t>
+          <t>2026-09-15 09:15</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10909</v>
+        <v>172.54</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-17 09:15</t>
+          <t>2026-09-18 11:45</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10994</v>
+        <v>172.89</v>
       </c>
       <c r="H9" t="n">
-        <v>10994</v>
+        <v>172.89</v>
       </c>
       <c r="I9" t="n">
-        <v>10909</v>
+        <v>168.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>418.2</v>
+        <v>1096.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-15 14:15</t>
+          <t>2026-09-15 11:15</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>417.4</v>
+        <v>1095.6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-17 11:15</t>
+          <t>2026-09-18 15:00</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>419.45</v>
+        <v>1132.4</v>
       </c>
       <c r="H10" t="n">
-        <v>419.45</v>
+        <v>1132.4</v>
       </c>
       <c r="I10" t="n">
-        <v>406</v>
+        <v>1081.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>122.65</v>
+        <v>462.15</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-15 14:00</t>
+          <t>2026-09-15 09:15</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>122.46</v>
+        <v>461.1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-17 11:30</t>
+          <t>2026-09-18 10:45</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>122.91</v>
+        <v>463.05</v>
       </c>
       <c r="H11" t="n">
-        <v>122.91</v>
+        <v>463.05</v>
       </c>
       <c r="I11" t="n">
-        <v>121.84</v>
+        <v>446.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4965</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-15 10:15</t>
+          <t>2026-09-15 11:45</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4956</v>
+        <v>80.06</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-17 10:15</t>
+          <t>2026-09-18 10:00</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4966.5</v>
+        <v>80.36</v>
       </c>
       <c r="H12" t="n">
-        <v>4966.5</v>
+        <v>80.36</v>
       </c>
       <c r="I12" t="n">
-        <v>4845</v>
+        <v>78.19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>630</v>
+        <v>521.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-15 10:45</t>
+          <t>2026-09-15 09:15</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>628.7</v>
+        <v>518.85</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-17 10:00</t>
+          <t>2026-09-18 15:00</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>631.6</v>
+        <v>526</v>
       </c>
       <c r="H13" t="n">
-        <v>631.6</v>
+        <v>526</v>
       </c>
       <c r="I13" t="n">
-        <v>611.6</v>
+        <v>503.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>973.1</v>
+        <v>1265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -939,64 +939,64 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>966.8</v>
+        <v>1252.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-17 09:15</t>
+          <t>2026-09-18 09:30</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>979.6</v>
+        <v>1273.9</v>
       </c>
       <c r="H14" t="n">
-        <v>979.6</v>
+        <v>1273.9</v>
       </c>
       <c r="I14" t="n">
-        <v>958.7</v>
+        <v>1227.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1443.7</v>
+        <v>3880.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-15 10:45</t>
+          <t>2026-09-15 09:15</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1443</v>
+        <v>3872.1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-17 09:15</t>
+          <t>2026-09-18 14:15</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1447</v>
+        <v>3884.9</v>
       </c>
       <c r="H15" t="n">
-        <v>1447</v>
+        <v>3884.9</v>
       </c>
       <c r="I15" t="n">
-        <v>1423.3</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1005,547 +1005,288 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4822</v>
+        <v>4275</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-15 14:15</t>
+          <t>2026-09-16 13:45</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4784</v>
+        <v>4266.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-17 11:45</t>
+          <t>2026-09-17 12:15</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4835.5</v>
+        <v>4276.1</v>
       </c>
       <c r="H16" t="n">
-        <v>4835.5</v>
+        <v>4276.1</v>
       </c>
       <c r="I16" t="n">
-        <v>4704.5</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>226.44</v>
+        <v>232.22</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-15 15:00</t>
+          <t>2026-09-17 13:15</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>226.4</v>
+        <v>232.15</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-17 09:15</t>
+          <t>2026-09-18 11:30</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>226.98</v>
+        <v>232.29</v>
       </c>
       <c r="H17" t="n">
-        <v>226.98</v>
+        <v>232.29</v>
       </c>
       <c r="I17" t="n">
-        <v>224.84</v>
+        <v>231.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3069.1</v>
+        <v>311.25</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-15 14:15</t>
+          <t>2026-09-15 14:45</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3058.1</v>
+        <v>311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-17 09:15</t>
+          <t>2026-09-18 15:15</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3102.1</v>
+        <v>312</v>
       </c>
       <c r="H18" t="n">
-        <v>3102.1</v>
+        <v>312</v>
       </c>
       <c r="I18" t="n">
-        <v>3029.5</v>
+        <v>308.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>160.12</v>
+        <v>992.4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-15 14:00</t>
+          <t>2026-09-15 09:15</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>160</v>
+        <v>989.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-17 09:15</t>
+          <t>2026-09-18 15:00</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>161.35</v>
+        <v>993.2</v>
       </c>
       <c r="H19" t="n">
-        <v>161.35</v>
+        <v>993.2</v>
       </c>
       <c r="I19" t="n">
-        <v>156.45</v>
+        <v>968</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>328.65</v>
+        <v>22370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-15 09:30</t>
+          <t>2026-09-15 11:30</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>328</v>
+        <v>22300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-17 15:15</t>
+          <t>2026-09-18 15:15</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>329.6</v>
+        <v>22600</v>
       </c>
       <c r="H20" t="n">
-        <v>329.6</v>
+        <v>22600</v>
       </c>
       <c r="I20" t="n">
-        <v>326.5</v>
+        <v>21665</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>232.22</v>
+        <v>3858.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-17 13:15</t>
+          <t>2026-09-15 10:15</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>232.15</v>
+        <v>3856.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-17 15:00</t>
+          <t>2026-09-18 15:15</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>232.4</v>
+        <v>3913.9</v>
       </c>
       <c r="H21" t="n">
-        <v>232.4</v>
+        <v>3913.9</v>
       </c>
       <c r="I21" t="n">
-        <v>231.3</v>
+        <v>3682.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1540.4</v>
+        <v>362.25</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-15 12:30</t>
+          <t>2026-09-16 09:30</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1540</v>
+        <v>361.55</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-17 12:00</t>
+          <t>2026-09-18 09:30</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1544</v>
+        <v>364.4</v>
       </c>
       <c r="H22" t="n">
-        <v>1544</v>
+        <v>364.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1521.1</v>
+        <v>360.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>362.25</v>
+        <v>165.16</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-16 09:30</t>
+          <t>2026-09-17 09:15</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>361.55</v>
+        <v>165.15</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-17 11:15</t>
+          <t>2026-09-18 15:15</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>362.4</v>
+        <v>166.83</v>
       </c>
       <c r="H23" t="n">
-        <v>362.4</v>
+        <v>166.83</v>
       </c>
       <c r="I23" t="n">
-        <v>360.4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>2185.5</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-09-16 14:30</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>2179.1</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-17 12:00</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>2188.9</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2188.9</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2163.2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4823</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-09-16 09:30</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>4798</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-17 14:15</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>4838.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4838.5</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4756</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>4062.8</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:15</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>4054.6</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-17 09:15</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>4123.7</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4123.7</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4002.4</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>UNITDSPR</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1384.3</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:00</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1383.7</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-17 15:00</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1390</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1390</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1368.7</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>VEDL</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>256.5</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-09-15 13:30</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>256</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-17 14:45</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>256.65</v>
-      </c>
-      <c r="H28" t="n">
-        <v>256.65</v>
-      </c>
-      <c r="I28" t="n">
-        <v>252.55</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>WIPRO</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>165.16</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-09-17 09:15</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>165.15</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-17 09:15</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>165.73</v>
-      </c>
-      <c r="H29" t="n">
-        <v>165.73</v>
-      </c>
-      <c r="I29" t="n">
-        <v>165.15</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1104.6</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-09-15 14:15</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>1103.8</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-17 09:15</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1110.6</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1110.6</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1086</v>
+        <v>163.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,112 +478,223 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1037.7</v>
+        <v>1005.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15</t>
+          <t>2026-09-22 13:15</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1031.8</v>
+        <v>1005.1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-21 15:00</t>
+          <t>2026-09-22 13:15</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1040.5</v>
+        <v>1010.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1040.5</v>
+        <v>1010.1</v>
       </c>
       <c r="I2" t="n">
-        <v>1030.5</v>
+        <v>1005.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>299.3</v>
+        <v>1338.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:30</t>
+          <t>2026-09-22 10:30</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>299.2</v>
+        <v>1338.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:30</t>
+          <t>2026-09-22 14:00</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>299.8</v>
+        <v>1343.9</v>
       </c>
       <c r="H3" t="n">
-        <v>299.8</v>
+        <v>1343.9</v>
       </c>
       <c r="I3" t="n">
-        <v>299.2</v>
+        <v>1333.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4155</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:15</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4095</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:45</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>4160.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4160.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4095</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>299.3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-09-21 10:30</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>299.2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:15</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>300.05</v>
+      </c>
+      <c r="H5" t="n">
+        <v>300.05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>298.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TCS</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>2101.2</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2026-09-21 09:15</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E6" t="n">
         <v>2078.4</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-09-21 09:15</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>2112</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2112</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:00</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2104</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I6" t="n">
         <v>2078.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:30</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>163.21</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:45</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>163.54</v>
+      </c>
+      <c r="H7" t="n">
+        <v>163.54</v>
+      </c>
+      <c r="I7" t="n">
+        <v>163.21</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,44 +478,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1005.5</v>
+        <v>11379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:15</t>
+          <t>2026-09-22 09:30</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1005.1</v>
+        <v>11373</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:15</t>
+          <t>2026-09-23 15:00</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1010.1</v>
+        <v>11424</v>
       </c>
       <c r="H2" t="n">
-        <v>1010.1</v>
+        <v>11424</v>
       </c>
       <c r="I2" t="n">
-        <v>1005.1</v>
+        <v>11282</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,177 +524,288 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1338.9</v>
+        <v>1832.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-22 10:30</t>
+          <t>2026-09-22 11:45</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1338.6</v>
+        <v>1831.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00</t>
+          <t>2026-09-22 14:15</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1343.9</v>
+        <v>1834.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1343.9</v>
+        <v>1834.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1333.8</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4155</v>
+        <v>1818.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-22 09:15</t>
+          <t>2026-09-22 13:00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4095</v>
+        <v>1818.2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-22 14:45</t>
+          <t>2026-09-23 09:15</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4160.7</v>
+        <v>1818.8</v>
       </c>
       <c r="H4" t="n">
-        <v>4160.7</v>
+        <v>1818.8</v>
       </c>
       <c r="I4" t="n">
-        <v>4095</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>299.3</v>
+        <v>3159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-21 10:30</t>
+          <t>2026-09-22 09:15</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>299.2</v>
+        <v>3153.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-22 15:15</t>
+          <t>2026-09-23 13:30</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>300.05</v>
+        <v>3161</v>
       </c>
       <c r="H5" t="n">
-        <v>300.05</v>
+        <v>3161</v>
       </c>
       <c r="I5" t="n">
-        <v>298.8</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2101.2</v>
+        <v>1338.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15</t>
+          <t>2026-09-22 10:30</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2078.4</v>
+        <v>1338.6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-22 15:00</t>
+          <t>2026-09-23 15:00</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2104</v>
+        <v>1340</v>
       </c>
       <c r="H6" t="n">
-        <v>2104</v>
+        <v>1340</v>
       </c>
       <c r="I6" t="n">
-        <v>2078.4</v>
+        <v>1333.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>163.3</v>
+        <v>3029.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-23 09:45</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3028.4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:45</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3032</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3032</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3022.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>2026-09-22 10:30</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>163.21</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-22 10:45</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>163.54</v>
-      </c>
-      <c r="H7" t="n">
-        <v>163.54</v>
-      </c>
-      <c r="I7" t="n">
-        <v>163.21</v>
+      <c r="E8" t="n">
+        <v>308.3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:15</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>309.15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>309.15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>307.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>986</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:15</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>984.1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:00</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>986.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>986.1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>984.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>299.3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-21 10:30</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>299.2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:15</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>300.85</v>
+      </c>
+      <c r="H10" t="n">
+        <v>300.85</v>
+      </c>
+      <c r="I10" t="n">
+        <v>298.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,81 +478,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11379</v>
+        <v>1832.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-22 09:30</t>
+          <t>2026-09-22 11:45</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11373</v>
+        <v>1831.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-23 15:00</t>
+          <t>2026-09-22 14:15</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>11424</v>
+        <v>1834.6</v>
       </c>
       <c r="H2" t="n">
-        <v>11424</v>
+        <v>1834.6</v>
       </c>
       <c r="I2" t="n">
-        <v>11282</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1832.1</v>
+        <v>1818.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-22 11:45</t>
+          <t>2026-09-22 13:00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1831.8</v>
+        <v>1818.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:15</t>
+          <t>2026-09-23 09:15</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1834.6</v>
+        <v>1818.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1834.6</v>
+        <v>1818.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1824</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,35 +561,35 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1818.6</v>
+        <v>3159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-22 13:00</t>
+          <t>2026-09-22 09:15</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1818.2</v>
+        <v>3153.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
+          <t>2026-09-23 13:30</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1818.8</v>
+        <v>3161</v>
       </c>
       <c r="H4" t="n">
-        <v>1818.8</v>
+        <v>3161</v>
       </c>
       <c r="I4" t="n">
-        <v>1813</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -598,35 +598,35 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3159</v>
+        <v>1338.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-22 09:15</t>
+          <t>2026-09-22 10:30</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3153.9</v>
+        <v>1338.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-23 13:30</t>
+          <t>2026-09-23 15:00</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3161</v>
+        <v>1340</v>
       </c>
       <c r="H5" t="n">
-        <v>3161</v>
+        <v>1340</v>
       </c>
       <c r="I5" t="n">
-        <v>3125</v>
+        <v>1333.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,35 +635,35 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1338.9</v>
+        <v>3029.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-22 10:30</t>
+          <t>2026-09-23 09:45</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1338.6</v>
+        <v>3028.4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-23 15:00</t>
+          <t>2026-09-23 14:45</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1340</v>
+        <v>3032</v>
       </c>
       <c r="H6" t="n">
-        <v>1340</v>
+        <v>3032</v>
       </c>
       <c r="I6" t="n">
-        <v>1333.8</v>
+        <v>3022.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -672,35 +672,35 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3029.5</v>
+        <v>308.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-23 09:45</t>
+          <t>2026-09-22 10:30</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3028.4</v>
+        <v>308.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-23 14:45</t>
+          <t>2026-09-23 09:15</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3032</v>
+        <v>309.15</v>
       </c>
       <c r="H7" t="n">
-        <v>3032</v>
+        <v>309.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3022.4</v>
+        <v>307.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -709,35 +709,35 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>308.5</v>
+        <v>986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-22 10:30</t>
+          <t>2026-09-22 15:15</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308.3</v>
+        <v>984.1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
+          <t>2026-09-23 10:00</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>309.15</v>
+        <v>986.1</v>
       </c>
       <c r="H8" t="n">
-        <v>309.15</v>
+        <v>986.1</v>
       </c>
       <c r="I8" t="n">
-        <v>307.1</v>
+        <v>984.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -746,65 +746,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>986</v>
+        <v>299.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-22 15:15</t>
+          <t>2026-09-21 10:30</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>984.1</v>
+        <v>299.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00</t>
+          <t>2026-09-23 09:15</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>986.1</v>
+        <v>300.85</v>
       </c>
       <c r="H9" t="n">
-        <v>986.1</v>
+        <v>300.85</v>
       </c>
       <c r="I9" t="n">
-        <v>984.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TMPV</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>299.3</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-09-21 10:30</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>299.2</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-23 09:15</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>300.85</v>
-      </c>
-      <c r="H10" t="n">
-        <v>300.85</v>
-      </c>
-      <c r="I10" t="n">
         <v>298.75</v>
       </c>
     </row>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -536,14 +536,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1818.8</v>
+        <v>1820.3</v>
       </c>
       <c r="H3" t="n">
-        <v>1818.8</v>
+        <v>1820.3</v>
       </c>
       <c r="I3" t="n">
         <v>1813</v>
@@ -557,7 +557,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -573,14 +573,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-23 13:30</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3161</v>
+        <v>3164.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3161</v>
+        <v>3164.4</v>
       </c>
       <c r="I4" t="n">
         <v>3125</v>
@@ -594,7 +594,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -610,17 +610,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-23 15:00</t>
+          <t>2026-09-24 14:45</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H5" t="n">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I5" t="n">
-        <v>1333.8</v>
+        <v>1330.2</v>
       </c>
     </row>
     <row r="6">
@@ -631,7 +631,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,17 +647,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-23 14:45</t>
+          <t>2026-09-24 11:00</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3032</v>
+        <v>3035</v>
       </c>
       <c r="H6" t="n">
-        <v>3032</v>
+        <v>3035</v>
       </c>
       <c r="I6" t="n">
-        <v>3022.4</v>
+        <v>3009.4</v>
       </c>
     </row>
     <row r="7">
@@ -668,7 +668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -684,14 +684,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
+          <t>2026-09-24 12:15</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>309.15</v>
+        <v>308.95</v>
       </c>
       <c r="H7" t="n">
-        <v>309.15</v>
+        <v>308.95</v>
       </c>
       <c r="I7" t="n">
         <v>307.1</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -721,17 +721,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00</t>
+          <t>2026-09-24 15:15</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>986.1</v>
+        <v>986.3</v>
       </c>
       <c r="H8" t="n">
-        <v>986.1</v>
+        <v>986.3</v>
       </c>
       <c r="I8" t="n">
-        <v>984.1</v>
+        <v>983</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -758,17 +758,313 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
+          <t>2026-09-24 11:45</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>300.85</v>
+        <v>299.35</v>
       </c>
       <c r="H9" t="n">
-        <v>300.85</v>
+        <v>299.35</v>
       </c>
       <c r="I9" t="n">
-        <v>298.75</v>
+        <v>298.65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1336.5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1335.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1340</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1340</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1335.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3159</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:15</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3153.9</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>3164.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3164.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>516.1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>514.25</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>518.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>518.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>514.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1927</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:45</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1925.9</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:30</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1928.7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1928.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1925.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>456.95</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>446.15</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>459.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>459.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>446.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>472</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:15</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>469.25</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:45</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>472.65</v>
+      </c>
+      <c r="H15" t="n">
+        <v>472.65</v>
+      </c>
+      <c r="I15" t="n">
+        <v>463.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1521.1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1520.9</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:00</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1533.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1533.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1517.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>986</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:15</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>984.1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:15</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>986.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>986.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>983</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,17 +647,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-24 11:00</t>
+          <t>2026-09-25 14:00</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3035</v>
+        <v>3038.9</v>
       </c>
       <c r="H6" t="n">
-        <v>3035</v>
+        <v>3038.9</v>
       </c>
       <c r="I6" t="n">
-        <v>3009.4</v>
+        <v>2967.1</v>
       </c>
     </row>
     <row r="7">
@@ -668,7 +668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -684,14 +684,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-24 12:15</t>
+          <t>2026-09-25 09:45</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>308.95</v>
+        <v>308.8</v>
       </c>
       <c r="H7" t="n">
-        <v>308.95</v>
+        <v>308.8</v>
       </c>
       <c r="I7" t="n">
         <v>307.1</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-24 15:15</t>
+          <t>2026-09-25 10:00</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -731,7 +731,7 @@
         <v>986.3</v>
       </c>
       <c r="I8" t="n">
-        <v>983</v>
+        <v>982.8</v>
       </c>
     </row>
     <row r="9">
@@ -779,7 +779,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -795,17 +795,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00</t>
+          <t>2026-09-25 15:00</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1340</v>
+        <v>1342.3</v>
       </c>
       <c r="H10" t="n">
-        <v>1340</v>
+        <v>1342.3</v>
       </c>
       <c r="I10" t="n">
-        <v>1335.9</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="11">
@@ -890,7 +890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-24 14:30</t>
+          <t>2026-09-25 13:30</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1928.7</v>
+        <v>1928.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1928.7</v>
+        <v>1928.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1925.5</v>
+        <v>1915.1</v>
       </c>
     </row>
     <row r="14">
@@ -964,7 +964,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -980,14 +980,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-24 12:45</t>
+          <t>2026-09-25 12:45</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>472.65</v>
+        <v>472.3</v>
       </c>
       <c r="H15" t="n">
-        <v>472.65</v>
+        <v>472.3</v>
       </c>
       <c r="I15" t="n">
         <v>463.7</v>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-24 15:15</t>
+          <t>2026-09-25 10:00</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1064,7 +1064,451 @@
         <v>986.3</v>
       </c>
       <c r="I17" t="n">
-        <v>983</v>
+        <v>982.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1336.5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1335.9</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:00</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1342.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1342.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2907</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:45</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2903.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:15</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2916.1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2916.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2898.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>200.4</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>200.19</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:15</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>200.43</v>
+      </c>
+      <c r="H20" t="n">
+        <v>200.43</v>
+      </c>
+      <c r="I20" t="n">
+        <v>196.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1219.9</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1191</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:00</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1220.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1220.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1175.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10821.29</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:30</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>10778</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:15</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>10833</v>
+      </c>
+      <c r="H22" t="n">
+        <v>10833</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10746</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4933</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:30</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4930.5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:15</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>4937.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4937.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4883.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1927</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:45</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1925.9</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:30</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1928.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1928.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1915.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3029.5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:45</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3028.4</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:00</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>3038.9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3038.9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2967.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1242.8</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1209.8</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:45</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1246.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1246.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1202.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>472</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:15</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>469.25</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:45</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>472.3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>472.3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>463.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:30</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>308.3</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:45</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>308.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>308.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>307.1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:30</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>163.21</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:15</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>163.45</v>
+      </c>
+      <c r="H29" t="n">
+        <v>163.45</v>
+      </c>
+      <c r="I29" t="n">
+        <v>161.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,1037 +478,593 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1832.1</v>
+        <v>196.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-22 11:45</t>
+          <t>2026-09-28 14:00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1831.8</v>
+        <v>196.05</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-22 14:15</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1834.6</v>
+        <v>196.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1834.6</v>
+        <v>196.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1824</v>
+        <v>195.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1818.6</v>
+        <v>8821.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-22 13:00</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1818.2</v>
+        <v>8814</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1820.3</v>
+        <v>8834</v>
       </c>
       <c r="H3" t="n">
-        <v>1820.3</v>
+        <v>8834</v>
       </c>
       <c r="I3" t="n">
-        <v>1813</v>
+        <v>8804.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3159</v>
+        <v>411.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-22 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3153.9</v>
+        <v>407.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3164.4</v>
+        <v>411.9</v>
       </c>
       <c r="H4" t="n">
-        <v>3164.4</v>
+        <v>411.9</v>
       </c>
       <c r="I4" t="n">
-        <v>3125</v>
+        <v>407.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1338.9</v>
+        <v>4883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-22 10:30</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1338.6</v>
+        <v>4880</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-24 14:45</t>
+          <t>2026-09-28 13:15</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1339</v>
+        <v>4892</v>
       </c>
       <c r="H5" t="n">
-        <v>1339</v>
+        <v>4892</v>
       </c>
       <c r="I5" t="n">
-        <v>1330.2</v>
+        <v>4869</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3029.5</v>
+        <v>1629.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-23 09:45</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3028.4</v>
+        <v>1625</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-25 14:00</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3038.9</v>
+        <v>1630</v>
       </c>
       <c r="H6" t="n">
-        <v>3038.9</v>
+        <v>1630</v>
       </c>
       <c r="I6" t="n">
-        <v>2967.1</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>308.5</v>
+        <v>1835.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-22 10:30</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308.3</v>
+        <v>1834.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>308.8</v>
+        <v>1845.9</v>
       </c>
       <c r="H7" t="n">
-        <v>308.8</v>
+        <v>1845.9</v>
       </c>
       <c r="I7" t="n">
-        <v>307.1</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>986</v>
+        <v>171.35</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-22 15:15</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>984.1</v>
+        <v>171.21</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-25 10:00</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>986.3</v>
+        <v>171.44</v>
       </c>
       <c r="H8" t="n">
-        <v>986.3</v>
+        <v>171.44</v>
       </c>
       <c r="I8" t="n">
-        <v>982.8</v>
+        <v>171.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>299.3</v>
+        <v>864.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-21 10:30</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>299.2</v>
+        <v>863.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-24 11:45</t>
+          <t>2026-09-28 11:45</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>299.35</v>
+        <v>866.7</v>
       </c>
       <c r="H9" t="n">
-        <v>299.35</v>
+        <v>866.7</v>
       </c>
       <c r="I9" t="n">
-        <v>298.65</v>
+        <v>859.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1336.5</v>
+        <v>906.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1335.9</v>
+        <v>899.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1342.3</v>
+        <v>909</v>
       </c>
       <c r="H10" t="n">
-        <v>1342.3</v>
+        <v>909</v>
       </c>
       <c r="I10" t="n">
-        <v>1315</v>
+        <v>889.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3159</v>
+        <v>991.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-22 09:15</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3153.9</v>
+        <v>989.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-28 11:15</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3164.4</v>
+        <v>993.3</v>
       </c>
       <c r="H11" t="n">
-        <v>3164.4</v>
+        <v>993.3</v>
       </c>
       <c r="I11" t="n">
-        <v>3125</v>
+        <v>986.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>516.1</v>
+        <v>399.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>514.25</v>
+        <v>396.65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 12:00</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>518.6</v>
+        <v>400.15</v>
       </c>
       <c r="H12" t="n">
-        <v>518.6</v>
+        <v>400.15</v>
       </c>
       <c r="I12" t="n">
-        <v>514.25</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1927</v>
+        <v>11975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-24 13:45</t>
+          <t>2026-09-28 11:00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1925.9</v>
+        <v>11965</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-25 13:30</t>
+          <t>2026-09-28 12:15</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1928.5</v>
+        <v>11980</v>
       </c>
       <c r="H13" t="n">
-        <v>1928.5</v>
+        <v>11980</v>
       </c>
       <c r="I13" t="n">
-        <v>1915.1</v>
+        <v>11945</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>456.95</v>
+        <v>1495.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>446.15</v>
+        <v>1495.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>459.3</v>
+        <v>1503</v>
       </c>
       <c r="H14" t="n">
-        <v>459.3</v>
+        <v>1503</v>
       </c>
       <c r="I14" t="n">
-        <v>446.15</v>
+        <v>1487.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>472</v>
+        <v>22165</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-22 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>469.25</v>
+        <v>22070</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-25 12:45</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>472.3</v>
+        <v>22170</v>
       </c>
       <c r="H15" t="n">
-        <v>472.3</v>
+        <v>22170</v>
       </c>
       <c r="I15" t="n">
-        <v>463.7</v>
+        <v>22070</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1521.1</v>
+        <v>1650.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1520.9</v>
+        <v>1637</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-24 14:00</t>
+          <t>2026-09-28 15:15</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1533.3</v>
+        <v>1655.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1533.3</v>
+        <v>1655.3</v>
       </c>
       <c r="I16" t="n">
-        <v>1517.5</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>986</v>
+        <v>10983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-22 15:15</t>
+          <t>2026-09-28 14:15</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>984.1</v>
+        <v>10981</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-25 10:00</t>
+          <t>2026-09-28 14:15</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>986.3</v>
+        <v>11002</v>
       </c>
       <c r="H17" t="n">
-        <v>986.3</v>
+        <v>11002</v>
       </c>
       <c r="I17" t="n">
-        <v>982.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1336.5</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-09-24 15:00</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1335.9</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-25 15:00</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1342.3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1342.3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2907</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-09-24 13:45</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2903.8</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-25 13:15</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>2916.1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2916.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2898.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ADANIPOWER</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>200.4</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-09-24 13:30</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>200.19</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-25 10:15</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>200.43</v>
-      </c>
-      <c r="H20" t="n">
-        <v>200.43</v>
-      </c>
-      <c r="I20" t="n">
-        <v>196.1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1219.9</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-09-24 09:15</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1191</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-25 14:00</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>1220.1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1220.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1175.1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>BAJAJHLDNG</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>10821.29</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-09-25 09:30</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>10778</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-25 12:15</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>10833</v>
-      </c>
-      <c r="H22" t="n">
-        <v>10833</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10746</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>4933</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-09-22 12:30</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>4930.5</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-25 15:15</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>4937.5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4937.5</v>
-      </c>
-      <c r="I23" t="n">
-        <v>4883.5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1927</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-09-24 13:45</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>1925.9</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-25 13:30</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>1928.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1928.5</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1915.1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>M&amp;M</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>3029.5</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-09-23 09:45</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>3028.4</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-25 14:00</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>3038.9</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3038.9</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2967.1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1242.8</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-09-24 09:15</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>1209.8</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-25 13:45</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1246.7</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1246.7</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1202.6</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>472</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-09-22 09:15</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>469.25</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-25 12:45</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>472.3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>472.3</v>
-      </c>
-      <c r="I27" t="n">
-        <v>463.7</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>RECLTD</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>308.5</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-09-22 10:30</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>308.3</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-25 09:45</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>308.8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>308.8</v>
-      </c>
-      <c r="I28" t="n">
-        <v>307.1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>WIPRO</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-09-22 10:30</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>163.21</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-25 13:15</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>163.45</v>
-      </c>
-      <c r="H29" t="n">
-        <v>163.45</v>
-      </c>
-      <c r="I29" t="n">
-        <v>161.67</v>
+        <v>10981</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -499,17 +499,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 12:45</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>196.4</v>
+        <v>197.47</v>
       </c>
       <c r="H2" t="n">
-        <v>196.4</v>
+        <v>197.47</v>
       </c>
       <c r="I2" t="n">
-        <v>195.37</v>
+        <v>192.45</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -573,17 +573,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 13:45</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>411.9</v>
+        <v>412.4</v>
       </c>
       <c r="H4" t="n">
-        <v>411.9</v>
+        <v>412.4</v>
       </c>
       <c r="I4" t="n">
-        <v>407.35</v>
+        <v>402.75</v>
       </c>
     </row>
     <row r="5">
@@ -631,7 +631,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,17 +647,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1630</v>
+        <v>1631.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1630</v>
+        <v>1631.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1621</v>
+        <v>1600.2</v>
       </c>
     </row>
     <row r="7">
@@ -705,7 +705,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -721,17 +721,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 11:45</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>171.44</v>
+        <v>171.66</v>
       </c>
       <c r="H8" t="n">
-        <v>171.44</v>
+        <v>171.66</v>
       </c>
       <c r="I8" t="n">
-        <v>171.05</v>
+        <v>168.57</v>
       </c>
     </row>
     <row r="9">
@@ -816,7 +816,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -832,17 +832,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-28 11:15</t>
+          <t>2026-09-29 15:15</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>993.3</v>
+        <v>1015.4</v>
       </c>
       <c r="H11" t="n">
-        <v>993.3</v>
+        <v>1015.4</v>
       </c>
       <c r="I11" t="n">
-        <v>986.6</v>
+        <v>980.4</v>
       </c>
     </row>
     <row r="12">
@@ -853,7 +853,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -869,17 +869,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-28 12:00</t>
+          <t>2026-09-29 10:30</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>400.15</v>
+        <v>400.3</v>
       </c>
       <c r="H12" t="n">
-        <v>400.15</v>
+        <v>400.3</v>
       </c>
       <c r="I12" t="n">
-        <v>396</v>
+        <v>394.7</v>
       </c>
     </row>
     <row r="13">
@@ -890,7 +890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-28 12:15</t>
+          <t>2026-09-29 11:45</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>11980</v>
+        <v>11995</v>
       </c>
       <c r="H13" t="n">
-        <v>11980</v>
+        <v>11995</v>
       </c>
       <c r="I13" t="n">
-        <v>11945</v>
+        <v>11832</v>
       </c>
     </row>
     <row r="14">
@@ -964,7 +964,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -980,17 +980,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 14:30</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>22170</v>
+        <v>22175</v>
       </c>
       <c r="H15" t="n">
-        <v>22170</v>
+        <v>22175</v>
       </c>
       <c r="I15" t="n">
-        <v>22070</v>
+        <v>22025</v>
       </c>
     </row>
     <row r="16">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15</t>
+          <t>2026-09-29 15:15</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1655.3</v>
+        <v>1654.7</v>
       </c>
       <c r="H16" t="n">
-        <v>1655.3</v>
+        <v>1654.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1637</v>
+        <v>1630.8</v>
       </c>
     </row>
     <row r="17">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1054,17 +1054,572 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-28 14:15</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>11002</v>
+        <v>11003</v>
       </c>
       <c r="H17" t="n">
-        <v>11002</v>
+        <v>11003</v>
       </c>
       <c r="I17" t="n">
-        <v>10981</v>
+        <v>10869</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2898.2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2855.6</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2972.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2972.9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2793.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1766.7</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1765.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1770.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1770.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1736.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:00</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>196.05</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:45</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>197.47</v>
+      </c>
+      <c r="H20" t="n">
+        <v>197.47</v>
+      </c>
+      <c r="I20" t="n">
+        <v>192.45</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2391</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2381.6</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:00</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>2401.4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2401.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2381.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>411.8</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>407.6</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:45</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>412.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>412.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>402.75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>991.6</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>989.8</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1015.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1015.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>980.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>78.73999999999999</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>80.26000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>80.26000000000001</v>
+      </c>
+      <c r="I24" t="n">
+        <v>77.09999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>263.55</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:00</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>264.3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>264.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>263.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1127.1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1127</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1134.3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1134.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1264.4</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1261.5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1272.4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1272.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>396.65</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:30</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>400.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>400.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>394.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1650.1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1637</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1654.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1654.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1630.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4848.5</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4844.5</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:45</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>4862.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4862.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4837</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4057</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4043.3</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>4081.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4081.4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4043.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>259</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>258.25</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>260</v>
+      </c>
+      <c r="H32" t="n">
+        <v>260</v>
+      </c>
+      <c r="I32" t="n">
+        <v>256.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,7 +557,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -573,14 +573,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-29 13:45</t>
+          <t>2026-09-30 10:45</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>412.4</v>
+        <v>412.6</v>
       </c>
       <c r="H4" t="n">
-        <v>412.4</v>
+        <v>412.6</v>
       </c>
       <c r="I4" t="n">
         <v>402.75</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,14 +647,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1631.4</v>
+        <v>1631.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1631.4</v>
+        <v>1631.6</v>
       </c>
       <c r="I6" t="n">
         <v>1600.2</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -721,14 +721,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-29 11:45</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>171.66</v>
+        <v>171.68</v>
       </c>
       <c r="H8" t="n">
-        <v>171.66</v>
+        <v>171.68</v>
       </c>
       <c r="I8" t="n">
         <v>168.57</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -906,14 +906,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-29 11:45</t>
+          <t>2026-09-30 09:30</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>11995</v>
+        <v>11999</v>
       </c>
       <c r="H13" t="n">
-        <v>11995</v>
+        <v>11999</v>
       </c>
       <c r="I13" t="n">
         <v>11832</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -980,17 +980,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-29 14:30</t>
+          <t>2026-09-30 12:15</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>22175</v>
+        <v>22190</v>
       </c>
       <c r="H15" t="n">
-        <v>22175</v>
+        <v>22190</v>
       </c>
       <c r="I15" t="n">
-        <v>22025</v>
+        <v>21585</v>
       </c>
     </row>
     <row r="16">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1017,14 +1017,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1654.7</v>
+        <v>1664.4</v>
       </c>
       <c r="H16" t="n">
-        <v>1654.7</v>
+        <v>1664.4</v>
       </c>
       <c r="I16" t="n">
         <v>1630.8</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15</t>
+          <t>2026-09-30 11:15</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2972.9</v>
+        <v>2901.9</v>
       </c>
       <c r="H18" t="n">
-        <v>2972.9</v>
+        <v>2901.9</v>
       </c>
       <c r="I18" t="n">
         <v>2793.7</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1239,14 +1239,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-29 13:45</t>
+          <t>2026-09-30 10:45</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>412.4</v>
+        <v>412.6</v>
       </c>
       <c r="H22" t="n">
-        <v>412.4</v>
+        <v>412.6</v>
       </c>
       <c r="I22" t="n">
         <v>402.75</v>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1313,14 +1313,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
+          <t>2026-09-30 11:30</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>80.26000000000001</v>
+        <v>79.91</v>
       </c>
       <c r="H24" t="n">
-        <v>80.26000000000001</v>
+        <v>79.91</v>
       </c>
       <c r="I24" t="n">
         <v>77.09999999999999</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1387,17 +1387,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
+          <t>2026-09-30 11:15</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1134.3</v>
+        <v>1130</v>
       </c>
       <c r="H26" t="n">
-        <v>1134.3</v>
+        <v>1130</v>
       </c>
       <c r="I26" t="n">
-        <v>1127</v>
+        <v>1125.1</v>
       </c>
     </row>
     <row r="27">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1424,14 +1424,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15</t>
+          <t>2026-09-30 12:00</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1272.4</v>
+        <v>1266.6</v>
       </c>
       <c r="H27" t="n">
-        <v>1272.4</v>
+        <v>1266.6</v>
       </c>
       <c r="I27" t="n">
         <v>1247</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1498,14 +1498,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1654.7</v>
+        <v>1664.4</v>
       </c>
       <c r="H29" t="n">
-        <v>1654.7</v>
+        <v>1664.4</v>
       </c>
       <c r="I29" t="n">
         <v>1630.8</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1609,17 +1609,1053 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
+          <t>2026-09-30 11:30</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>260</v>
+        <v>259.35</v>
       </c>
       <c r="H32" t="n">
-        <v>260</v>
+        <v>259.35</v>
       </c>
       <c r="I32" t="n">
         <v>256.15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1315</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:15</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1336</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1336</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1275.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2898.2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2855.6</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:15</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>2901.9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2901.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2793.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1270.2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:15</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1247</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:15</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1272.9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1272.9</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1223.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10738</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>10717</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:30</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>10756</v>
+      </c>
+      <c r="H36" t="n">
+        <v>10756</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10600</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>232.52</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>232.24</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>234.2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>234.2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>223.95</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>387.25</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:45</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>389.2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>389.2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>382.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>411.8</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>407.6</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:45</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>402.75</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>47145</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-09-28 11:30</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>46940</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:30</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>47165</v>
+      </c>
+      <c r="H40" t="n">
+        <v>47165</v>
+      </c>
+      <c r="I40" t="n">
+        <v>45700</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>381.55</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>379.3</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:15</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>383.15</v>
+      </c>
+      <c r="H41" t="n">
+        <v>383.15</v>
+      </c>
+      <c r="I41" t="n">
+        <v>378.05</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>9312.5</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:15</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>9288</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:45</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>9321</v>
+      </c>
+      <c r="H42" t="n">
+        <v>9321</v>
+      </c>
+      <c r="I42" t="n">
+        <v>9280</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>171.35</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:15</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>171.21</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:30</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>171.68</v>
+      </c>
+      <c r="H43" t="n">
+        <v>171.68</v>
+      </c>
+      <c r="I43" t="n">
+        <v>168.57</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1234.6</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:45</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1233.3</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1247.4</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1247.4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>514</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:00</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:15</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>515.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>515.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>513.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1312</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1306.5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:30</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1313.8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1313.8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1291.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>445.35</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:30</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>445.85</v>
+      </c>
+      <c r="H47" t="n">
+        <v>445.85</v>
+      </c>
+      <c r="I47" t="n">
+        <v>442.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>721.95</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>714.5</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:00</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>722.35</v>
+      </c>
+      <c r="H48" t="n">
+        <v>722.35</v>
+      </c>
+      <c r="I48" t="n">
+        <v>704.8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>457.7</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>455.5</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:30</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>460</v>
+      </c>
+      <c r="H49" t="n">
+        <v>460</v>
+      </c>
+      <c r="I49" t="n">
+        <v>448.55</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>78.73999999999999</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:30</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>79.91</v>
+      </c>
+      <c r="H50" t="n">
+        <v>79.91</v>
+      </c>
+      <c r="I50" t="n">
+        <v>77.09999999999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1127.1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1127</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:15</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1130</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1130</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1125.1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1264.4</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1261.5</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:00</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1266.6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1266.6</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3996</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3936</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>4072.1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4072.1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>159.85</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:00</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>161.09</v>
+      </c>
+      <c r="H54" t="n">
+        <v>161.09</v>
+      </c>
+      <c r="I54" t="n">
+        <v>159.41</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>22165</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>22070</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:15</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>22190</v>
+      </c>
+      <c r="H55" t="n">
+        <v>22190</v>
+      </c>
+      <c r="I55" t="n">
+        <v>21585</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1832.2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1831.7</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:15</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1833.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1833.5</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1814.2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1650.1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1637</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1664.4</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1664.4</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1630.8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1525.1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1523.2</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1546.9</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1546.9</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1510.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>259</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>258.25</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:30</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="H59" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="I59" t="n">
+        <v>256.15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1152.1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:30</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1149.5</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:45</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1154.7</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1154.7</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1149.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,14 +721,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>171.68</v>
+        <v>172.3</v>
       </c>
       <c r="H8" t="n">
-        <v>171.68</v>
+        <v>172.3</v>
       </c>
       <c r="I8" t="n">
         <v>168.57</v>
@@ -906,14 +906,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-30 09:30</t>
+          <t>2026-09-30 13:45</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>11999</v>
+        <v>11976</v>
       </c>
       <c r="H13" t="n">
-        <v>11999</v>
+        <v>11976</v>
       </c>
       <c r="I13" t="n">
         <v>11832</v>
@@ -980,14 +980,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-30 12:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>22190</v>
+        <v>22345</v>
       </c>
       <c r="H15" t="n">
-        <v>22190</v>
+        <v>22345</v>
       </c>
       <c r="I15" t="n">
         <v>21585</v>
@@ -1017,14 +1017,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 13:45</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1664.4</v>
+        <v>1658</v>
       </c>
       <c r="H16" t="n">
-        <v>1664.4</v>
+        <v>1658</v>
       </c>
       <c r="I16" t="n">
         <v>1630.8</v>
@@ -1091,14 +1091,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-30 11:15</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2901.9</v>
+        <v>2903.4</v>
       </c>
       <c r="H18" t="n">
-        <v>2901.9</v>
+        <v>2903.4</v>
       </c>
       <c r="I18" t="n">
         <v>2793.7</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1202,14 +1202,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-29 10:00</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2401.4</v>
+        <v>2402.6</v>
       </c>
       <c r="H21" t="n">
-        <v>2401.4</v>
+        <v>2402.6</v>
       </c>
       <c r="I21" t="n">
         <v>2381.6</v>
@@ -1387,14 +1387,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-30 11:15</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1130</v>
+        <v>1134.9</v>
       </c>
       <c r="H26" t="n">
-        <v>1130</v>
+        <v>1134.9</v>
       </c>
       <c r="I26" t="n">
         <v>1125.1</v>
@@ -1424,14 +1424,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1266.6</v>
+        <v>1265.3</v>
       </c>
       <c r="H27" t="n">
-        <v>1266.6</v>
+        <v>1265.3</v>
       </c>
       <c r="I27" t="n">
         <v>1247</v>
@@ -1498,14 +1498,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 13:45</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1664.4</v>
+        <v>1658</v>
       </c>
       <c r="H29" t="n">
-        <v>1664.4</v>
+        <v>1658</v>
       </c>
       <c r="I29" t="n">
         <v>1630.8</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-30 11:30</t>
+          <t>2026-09-30 12:45</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1683,14 +1683,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-30 11:15</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2901.9</v>
+        <v>2903.4</v>
       </c>
       <c r="H34" t="n">
-        <v>2901.9</v>
+        <v>2903.4</v>
       </c>
       <c r="I34" t="n">
         <v>2793.7</v>
@@ -1720,14 +1720,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-30 11:15</t>
+          <t>2026-09-30 14:30</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1272.9</v>
+        <v>1271</v>
       </c>
       <c r="H35" t="n">
-        <v>1272.9</v>
+        <v>1271</v>
       </c>
       <c r="I35" t="n">
         <v>1223.9</v>
@@ -1757,14 +1757,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-30 11:30</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>10756</v>
+        <v>10788</v>
       </c>
       <c r="H36" t="n">
-        <v>10756</v>
+        <v>10788</v>
       </c>
       <c r="I36" t="n">
         <v>10600</v>
@@ -1905,14 +1905,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30</t>
+          <t>2026-09-30 14:45</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>47165</v>
+        <v>47230</v>
       </c>
       <c r="H40" t="n">
-        <v>47165</v>
+        <v>47230</v>
       </c>
       <c r="I40" t="n">
         <v>45700</v>
@@ -1942,14 +1942,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-30 12:15</t>
+          <t>2026-09-30 14:45</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>383.15</v>
+        <v>381.65</v>
       </c>
       <c r="H41" t="n">
-        <v>383.15</v>
+        <v>381.65</v>
       </c>
       <c r="I41" t="n">
         <v>378.05</v>
@@ -1979,14 +1979,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-30 11:45</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>9321</v>
+        <v>9313.5</v>
       </c>
       <c r="H42" t="n">
-        <v>9321</v>
+        <v>9313.5</v>
       </c>
       <c r="I42" t="n">
         <v>9280</v>
@@ -2016,14 +2016,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>171.68</v>
+        <v>172.3</v>
       </c>
       <c r="H43" t="n">
-        <v>171.68</v>
+        <v>172.3</v>
       </c>
       <c r="I43" t="n">
         <v>168.57</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>445.85</v>
+        <v>445.65</v>
       </c>
       <c r="H47" t="n">
-        <v>445.85</v>
+        <v>445.65</v>
       </c>
       <c r="I47" t="n">
         <v>442.8</v>
@@ -2312,14 +2312,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-30 11:15</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1130</v>
+        <v>1134.9</v>
       </c>
       <c r="H51" t="n">
-        <v>1130</v>
+        <v>1134.9</v>
       </c>
       <c r="I51" t="n">
         <v>1125.1</v>
@@ -2349,14 +2349,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1266.6</v>
+        <v>1265.3</v>
       </c>
       <c r="H52" t="n">
-        <v>1266.6</v>
+        <v>1265.3</v>
       </c>
       <c r="I52" t="n">
         <v>1247</v>
@@ -2386,14 +2386,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>4072.1</v>
+        <v>4008</v>
       </c>
       <c r="H53" t="n">
-        <v>4072.1</v>
+        <v>4008</v>
       </c>
       <c r="I53" t="n">
         <v>3936</v>
@@ -2460,14 +2460,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-30 12:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>22190</v>
+        <v>22345</v>
       </c>
       <c r="H55" t="n">
-        <v>22190</v>
+        <v>22345</v>
       </c>
       <c r="I55" t="n">
         <v>21585</v>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-30 12:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1833.5</v>
+        <v>1845</v>
       </c>
       <c r="H56" t="n">
-        <v>1833.5</v>
+        <v>1845</v>
       </c>
       <c r="I56" t="n">
         <v>1814.2</v>
@@ -2534,14 +2534,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 13:45</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1664.4</v>
+        <v>1658</v>
       </c>
       <c r="H57" t="n">
-        <v>1664.4</v>
+        <v>1658</v>
       </c>
       <c r="I57" t="n">
         <v>1630.8</v>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-30 11:30</t>
+          <t>2026-09-30 12:45</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2655,6 +2655,598 @@
         <v>1154.7</v>
       </c>
       <c r="I60" t="n">
+        <v>1149.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2898.2</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2855.6</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:15</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>2903.4</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2903.4</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2793.7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1270.2</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:15</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1247</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:30</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1271</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1271</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1223.9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2391</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2381.6</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:15</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>2402.6</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2402.6</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2381.6</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>10738</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>10717</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:15</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>10788</v>
+      </c>
+      <c r="H64" t="n">
+        <v>10788</v>
+      </c>
+      <c r="I64" t="n">
+        <v>10600</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>411.8</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>407.6</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:45</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="H65" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="I65" t="n">
+        <v>402.75</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>514</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:00</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:15</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>515.5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>515.5</v>
+      </c>
+      <c r="I66" t="n">
+        <v>513.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1312</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1306.5</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:30</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1313.8</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1313.8</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1291.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>721.95</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>714.5</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:00</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>722.35</v>
+      </c>
+      <c r="H68" t="n">
+        <v>722.35</v>
+      </c>
+      <c r="I68" t="n">
+        <v>704.8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>78.73999999999999</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:30</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>79.91</v>
+      </c>
+      <c r="H69" t="n">
+        <v>79.91</v>
+      </c>
+      <c r="I69" t="n">
+        <v>77.09999999999999</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1127.1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1127</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:15</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1134.9</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1134.9</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1125.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1127</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:45</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1126.7</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:15</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1135</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1135</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1091.9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3996</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3936</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:00</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>4008</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4008</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>159.85</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:00</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>161.09</v>
+      </c>
+      <c r="H73" t="n">
+        <v>161.09</v>
+      </c>
+      <c r="I73" t="n">
+        <v>159.41</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>22165</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>22070</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:00</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>22345</v>
+      </c>
+      <c r="H74" t="n">
+        <v>22345</v>
+      </c>
+      <c r="I74" t="n">
+        <v>21585</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1650.1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1637</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:45</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1658</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1658</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1630.8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1152.1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:30</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1149.5</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:45</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1154.7</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1154.7</v>
+      </c>
+      <c r="I76" t="n">
         <v>1149.5</v>
       </c>
     </row>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -499,14 +499,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>197.47</v>
+        <v>197.15</v>
       </c>
       <c r="H2" t="n">
-        <v>197.47</v>
+        <v>197.15</v>
       </c>
       <c r="I2" t="n">
         <v>192.45</v>
@@ -557,7 +557,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -573,14 +573,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-30 10:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>412.6</v>
+        <v>413.2</v>
       </c>
       <c r="H4" t="n">
-        <v>412.6</v>
+        <v>413.2</v>
       </c>
       <c r="I4" t="n">
         <v>402.75</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -721,14 +721,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-30 15:00</t>
+          <t>2026-10-01 10:45</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>172.3</v>
+        <v>171.38</v>
       </c>
       <c r="H8" t="n">
-        <v>172.3</v>
+        <v>171.38</v>
       </c>
       <c r="I8" t="n">
         <v>168.57</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-30 13:45</t>
+          <t>2026-10-01 14:30</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1658</v>
+        <v>1662.7</v>
       </c>
       <c r="H16" t="n">
-        <v>1658</v>
+        <v>1662.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1630.8</v>
+        <v>1618.1</v>
       </c>
     </row>
     <row r="17">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-29 14:45</t>
+          <t>2026-10-01 11:30</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1770.2</v>
+        <v>1768.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1770.2</v>
+        <v>1768.6</v>
       </c>
       <c r="I19" t="n">
         <v>1736.8</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1165,14 +1165,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>197.47</v>
+        <v>197.15</v>
       </c>
       <c r="H20" t="n">
-        <v>197.47</v>
+        <v>197.15</v>
       </c>
       <c r="I20" t="n">
         <v>192.45</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15</t>
+          <t>2026-10-01 15:15</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2402.6</v>
+        <v>2407</v>
       </c>
       <c r="H21" t="n">
-        <v>2402.6</v>
+        <v>2407</v>
       </c>
       <c r="I21" t="n">
-        <v>2381.6</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="22">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1239,14 +1239,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-30 10:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>412.6</v>
+        <v>413.2</v>
       </c>
       <c r="H22" t="n">
-        <v>412.6</v>
+        <v>413.2</v>
       </c>
       <c r="I22" t="n">
         <v>402.75</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1498,17 +1498,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-30 13:45</t>
+          <t>2026-10-01 14:30</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1658</v>
+        <v>1662.7</v>
       </c>
       <c r="H29" t="n">
-        <v>1658</v>
+        <v>1662.7</v>
       </c>
       <c r="I29" t="n">
-        <v>1630.8</v>
+        <v>1618.1</v>
       </c>
     </row>
     <row r="30">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1646,14 +1646,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 14:15</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1336</v>
+        <v>1319.3</v>
       </c>
       <c r="H33" t="n">
-        <v>1336</v>
+        <v>1319.3</v>
       </c>
       <c r="I33" t="n">
         <v>1275.8</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1720,14 +1720,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-30 14:30</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1271</v>
+        <v>1279.8</v>
       </c>
       <c r="H35" t="n">
-        <v>1271</v>
+        <v>1279.8</v>
       </c>
       <c r="I35" t="n">
         <v>1223.9</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1794,14 +1794,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 11:15</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>234.2</v>
+        <v>232.6</v>
       </c>
       <c r="H37" t="n">
-        <v>234.2</v>
+        <v>232.6</v>
       </c>
       <c r="I37" t="n">
         <v>223.95</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1868,14 +1868,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-30 10:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>412.6</v>
+        <v>413.2</v>
       </c>
       <c r="H39" t="n">
-        <v>412.6</v>
+        <v>413.2</v>
       </c>
       <c r="I39" t="n">
         <v>402.75</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1942,14 +1942,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-30 14:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>381.65</v>
+        <v>382.3</v>
       </c>
       <c r="H41" t="n">
-        <v>381.65</v>
+        <v>382.3</v>
       </c>
       <c r="I41" t="n">
         <v>378.05</v>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2016,14 +2016,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-30 15:00</t>
+          <t>2026-10-01 10:45</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>172.3</v>
+        <v>171.38</v>
       </c>
       <c r="H43" t="n">
-        <v>172.3</v>
+        <v>171.38</v>
       </c>
       <c r="I43" t="n">
         <v>168.57</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2053,14 +2053,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 14:15</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1247.4</v>
+        <v>1234.7</v>
       </c>
       <c r="H44" t="n">
-        <v>1247.4</v>
+        <v>1234.7</v>
       </c>
       <c r="I44" t="n">
         <v>1222</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2127,14 +2127,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-30 09:30</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1313.8</v>
+        <v>1314.5</v>
       </c>
       <c r="H46" t="n">
-        <v>1313.8</v>
+        <v>1314.5</v>
       </c>
       <c r="I46" t="n">
         <v>1291.1</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2164,17 +2164,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30</t>
+          <t>2026-10-01 14:15</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>445.65</v>
+        <v>446.25</v>
       </c>
       <c r="H47" t="n">
-        <v>445.65</v>
+        <v>446.25</v>
       </c>
       <c r="I47" t="n">
-        <v>442.8</v>
+        <v>441.8</v>
       </c>
     </row>
     <row r="48">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-30 11:30</t>
+          <t>2026-10-01 13:00</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>460</v>
+        <v>459.7</v>
       </c>
       <c r="H49" t="n">
-        <v>460</v>
+        <v>459.7</v>
       </c>
       <c r="I49" t="n">
-        <v>448.55</v>
+        <v>447.25</v>
       </c>
     </row>
     <row r="50">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-30 15:00</t>
+          <t>2026-10-01 15:00</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>4008</v>
+        <v>4006.3</v>
       </c>
       <c r="H53" t="n">
-        <v>4008</v>
+        <v>4006.3</v>
       </c>
       <c r="I53" t="n">
         <v>3936</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2423,17 +2423,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-29 11:00</t>
+          <t>2026-10-01 11:30</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>161.09</v>
+        <v>160.55</v>
       </c>
       <c r="H54" t="n">
-        <v>161.09</v>
+        <v>160.55</v>
       </c>
       <c r="I54" t="n">
-        <v>159.41</v>
+        <v>158.51</v>
       </c>
     </row>
     <row r="55">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2534,17 +2534,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-30 13:45</t>
+          <t>2026-10-01 14:30</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1658</v>
+        <v>1662.7</v>
       </c>
       <c r="H57" t="n">
-        <v>1658</v>
+        <v>1662.7</v>
       </c>
       <c r="I57" t="n">
-        <v>1630.8</v>
+        <v>1618.1</v>
       </c>
     </row>
     <row r="58">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2571,14 +2571,14 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 14:30</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1546.9</v>
+        <v>1530.8</v>
       </c>
       <c r="H58" t="n">
-        <v>1546.9</v>
+        <v>1530.8</v>
       </c>
       <c r="I58" t="n">
         <v>1510.5</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -2719,14 +2719,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-30 14:30</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1271</v>
+        <v>1279.8</v>
       </c>
       <c r="H62" t="n">
-        <v>1271</v>
+        <v>1279.8</v>
       </c>
       <c r="I62" t="n">
         <v>1223.9</v>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15</t>
+          <t>2026-10-01 15:15</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>2402.6</v>
+        <v>2407</v>
       </c>
       <c r="H63" t="n">
-        <v>2402.6</v>
+        <v>2407</v>
       </c>
       <c r="I63" t="n">
-        <v>2381.6</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="64">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2830,14 +2830,14 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-30 10:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>412.6</v>
+        <v>413.2</v>
       </c>
       <c r="H65" t="n">
-        <v>412.6</v>
+        <v>413.2</v>
       </c>
       <c r="I65" t="n">
         <v>402.75</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2904,14 +2904,14 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-30 09:30</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1313.8</v>
+        <v>1314.5</v>
       </c>
       <c r="H67" t="n">
-        <v>1313.8</v>
+        <v>1314.5</v>
       </c>
       <c r="I67" t="n">
         <v>1291.1</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -3089,14 +3089,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-30 15:00</t>
+          <t>2026-10-01 15:00</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>4008</v>
+        <v>4006.3</v>
       </c>
       <c r="H72" t="n">
-        <v>4008</v>
+        <v>4006.3</v>
       </c>
       <c r="I72" t="n">
         <v>3936</v>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-29 11:00</t>
+          <t>2026-10-01 11:30</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>161.09</v>
+        <v>160.55</v>
       </c>
       <c r="H73" t="n">
-        <v>161.09</v>
+        <v>160.55</v>
       </c>
       <c r="I73" t="n">
-        <v>159.41</v>
+        <v>158.51</v>
       </c>
     </row>
     <row r="74">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-30 13:45</t>
+          <t>2026-10-01 14:30</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1658</v>
+        <v>1662.7</v>
       </c>
       <c r="H75" t="n">
-        <v>1658</v>
+        <v>1662.7</v>
       </c>
       <c r="I75" t="n">
-        <v>1630.8</v>
+        <v>1618.1</v>
       </c>
     </row>
     <row r="76">
@@ -3248,6 +3248,487 @@
       </c>
       <c r="I76" t="n">
         <v>1149.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1315</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:15</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:15</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1319.3</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1319.3</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1275.8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1270.2</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:15</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1247</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:45</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1279.8</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1279.8</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1223.9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:00</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>196.05</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:45</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>197.15</v>
+      </c>
+      <c r="H79" t="n">
+        <v>197.15</v>
+      </c>
+      <c r="I79" t="n">
+        <v>192.45</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2391</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>2381.6</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:15</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>2407</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2407</v>
+      </c>
+      <c r="I80" t="n">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>411.8</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>407.6</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:15</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>413.2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>413.2</v>
+      </c>
+      <c r="I81" t="n">
+        <v>402.75</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>871.1</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:00</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>879</v>
+      </c>
+      <c r="H82" t="n">
+        <v>879</v>
+      </c>
+      <c r="I82" t="n">
+        <v>854.2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1234.6</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:45</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1233.3</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:15</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>445.35</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:15</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>446.25</v>
+      </c>
+      <c r="H84" t="n">
+        <v>446.25</v>
+      </c>
+      <c r="I84" t="n">
+        <v>441.8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3996</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>3936</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:00</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>4006.3</v>
+      </c>
+      <c r="H85" t="n">
+        <v>4006.3</v>
+      </c>
+      <c r="I85" t="n">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1699.9</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:15</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1695.5</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:00</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>1705.5</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1705.5</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1677.7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1650.1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1637</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:30</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1662.7</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1662.7</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1618.1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1525.1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1523.2</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:30</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1530.8</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1530.8</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1510.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>422</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>421.25</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:30</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>422.85</v>
+      </c>
+      <c r="H89" t="n">
+        <v>422.85</v>
+      </c>
+      <c r="I89" t="n">
+        <v>415.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,44 +478,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>378.65</v>
+        <v>7910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-05 09:30</t>
+          <t>2026-10-06 09:15</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>377.05</v>
+        <v>7807.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-05 12:15</t>
+          <t>2026-10-06 15:15</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>380</v>
+        <v>7914.5</v>
       </c>
       <c r="H2" t="n">
-        <v>380</v>
+        <v>7914.5</v>
       </c>
       <c r="I2" t="n">
-        <v>377.05</v>
+        <v>7807.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,72 +524,72 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>296.5</v>
+        <v>378.65</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-05 11:15</t>
+          <t>2026-10-05 09:30</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>295.1</v>
+        <v>377.05</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-05 15:00</t>
+          <t>2026-10-05 12:15</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>296.95</v>
+        <v>380</v>
       </c>
       <c r="H3" t="n">
-        <v>296.95</v>
+        <v>380</v>
       </c>
       <c r="I3" t="n">
-        <v>294.55</v>
+        <v>377.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4737</v>
+        <v>296.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-05 11:15</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4734.1</v>
+        <v>295.1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-06 14:45</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4748.8</v>
+        <v>299.2</v>
       </c>
       <c r="H4" t="n">
-        <v>4748.8</v>
+        <v>299.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4734.1</v>
+        <v>294.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -598,35 +598,35 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1333.4</v>
+        <v>4737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1321.9</v>
+        <v>4734.1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:45</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1333.5</v>
+        <v>4748.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1333.5</v>
+        <v>4748.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1321.3</v>
+        <v>4734.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1194.9</v>
+        <v>1333.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -643,27 +643,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1189.9</v>
+        <v>1321.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-05 15:15</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1200</v>
+        <v>1335.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1200</v>
+        <v>1335.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1189.9</v>
+        <v>1321.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5051</v>
+        <v>1194.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -680,132 +680,798 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5034.5</v>
+        <v>1189.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:45</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5086</v>
+        <v>1200</v>
       </c>
       <c r="H7" t="n">
-        <v>5086</v>
+        <v>1200</v>
       </c>
       <c r="I7" t="n">
-        <v>4995.5</v>
+        <v>1189.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1295</v>
+        <v>5051</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1293</v>
+        <v>5034.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-05 14:15</t>
+          <t>2026-10-06 09:45</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1297</v>
+        <v>5070.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1297</v>
+        <v>5070.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1293</v>
+        <v>4995.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4717.3</v>
+        <v>1295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-05 10:15</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4715.6</v>
+        <v>1293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-05 11:45</t>
+          <t>2026-10-06 12:00</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4730.4</v>
+        <v>1296</v>
       </c>
       <c r="H9" t="n">
-        <v>4730.4</v>
+        <v>1296</v>
       </c>
       <c r="I9" t="n">
-        <v>4710</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1510.5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1508.4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:30</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1510.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1510.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1505.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4717.3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:15</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4715.6</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>4751.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4751.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4702.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>TVSMOTOR</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C12" t="n">
         <v>3930.1</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E12" t="n">
         <v>3920</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G12" t="n">
         <v>3938</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H12" t="n">
         <v>3938</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I12" t="n">
         <v>3920</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>7910</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>7807.5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:15</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>7914.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7914.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7807.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2377</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:00</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2373.1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:30</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>2381.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2381.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2336.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>296.5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:15</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>295.1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:45</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>299.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>299.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>294.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1333.4</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:15</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1321.9</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:15</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1335.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1335.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1321.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>168.43</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:00</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>168.85</v>
+      </c>
+      <c r="H17" t="n">
+        <v>168.85</v>
+      </c>
+      <c r="I17" t="n">
+        <v>166.48</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2944.4</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:45</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2941.5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:30</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2952.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2952.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2936.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>706.25</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:15</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>705.6</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:45</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>708.35</v>
+      </c>
+      <c r="H19" t="n">
+        <v>708.35</v>
+      </c>
+      <c r="I19" t="n">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5051</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:15</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5034.5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:45</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>5070.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5070.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4995.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>131.02</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:15</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>130.51</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:45</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="I21" t="n">
+        <v>129.72</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>76.51000000000001</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:00</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>76.41</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="H22" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="I22" t="n">
+        <v>76.06999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1079</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1035.8</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:45</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1081.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1081.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1035.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>902.05</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>892.9</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:00</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>902.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>902.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>892.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1295</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:00</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1293</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:00</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1296</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1296</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3709.5</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:00</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3708</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>3721.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3721.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3695</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1792.6</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:15</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1785.4</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:00</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1794.4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1794.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1769.1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4717.3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:15</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4715.6</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>4751.2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4751.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4702.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -499,14 +499,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:15</t>
+          <t>2026-10-07 15:00</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7914.5</v>
+        <v>7917</v>
       </c>
       <c r="H2" t="n">
-        <v>7914.5</v>
+        <v>7917</v>
       </c>
       <c r="I2" t="n">
         <v>7807.5</v>
@@ -520,7 +520,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -536,14 +536,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-05 12:15</t>
+          <t>2026-10-07 14:45</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>380</v>
+        <v>378.9</v>
       </c>
       <c r="H3" t="n">
-        <v>380</v>
+        <v>378.9</v>
       </c>
       <c r="I3" t="n">
         <v>377.05</v>
@@ -557,7 +557,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -573,14 +573,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-06 14:45</t>
+          <t>2026-10-07 13:15</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>299.2</v>
+        <v>296.6</v>
       </c>
       <c r="H4" t="n">
-        <v>299.2</v>
+        <v>296.6</v>
       </c>
       <c r="I4" t="n">
         <v>294.55</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,14 +647,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-05 15:15</t>
+          <t>2026-10-07 14:15</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1335.5</v>
+        <v>1333.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1335.5</v>
+        <v>1333.6</v>
       </c>
       <c r="I6" t="n">
         <v>1321.3</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -684,14 +684,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 14:30</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1200</v>
+        <v>1196.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1200</v>
+        <v>1196.2</v>
       </c>
       <c r="I7" t="n">
         <v>1189.9</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -795,17 +795,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-06 10:30</t>
+          <t>2026-10-07 10:45</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1510.7</v>
+        <v>1510.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1510.7</v>
+        <v>1510.6</v>
       </c>
       <c r="I10" t="n">
-        <v>1505.4</v>
+        <v>1493.6</v>
       </c>
     </row>
     <row r="11">
@@ -816,7 +816,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -832,14 +832,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-06 09:30</t>
+          <t>2026-10-07 12:00</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4751.2</v>
+        <v>4728.1</v>
       </c>
       <c r="H11" t="n">
-        <v>4751.2</v>
+        <v>4728.1</v>
       </c>
       <c r="I11" t="n">
         <v>4702.5</v>
@@ -853,7 +853,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -869,17 +869,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 14:30</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3938</v>
+        <v>3931</v>
       </c>
       <c r="H12" t="n">
-        <v>3938</v>
+        <v>3931</v>
       </c>
       <c r="I12" t="n">
-        <v>3920</v>
+        <v>3870.8</v>
       </c>
     </row>
     <row r="13">
@@ -890,7 +890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -906,14 +906,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-06 15:15</t>
+          <t>2026-10-07 15:00</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>7914.5</v>
+        <v>7917</v>
       </c>
       <c r="H13" t="n">
-        <v>7914.5</v>
+        <v>7917</v>
       </c>
       <c r="I13" t="n">
         <v>7807.5</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -943,14 +943,14 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06 11:30</t>
+          <t>2026-10-07 10:15</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2381.5</v>
+        <v>2388.8</v>
       </c>
       <c r="H14" t="n">
-        <v>2381.5</v>
+        <v>2388.8</v>
       </c>
       <c r="I14" t="n">
         <v>2336.9</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -980,14 +980,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-06 14:45</t>
+          <t>2026-10-07 13:15</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>299.2</v>
+        <v>296.6</v>
       </c>
       <c r="H15" t="n">
-        <v>299.2</v>
+        <v>296.6</v>
       </c>
       <c r="I15" t="n">
         <v>294.55</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1017,14 +1017,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-05 15:15</t>
+          <t>2026-10-07 14:15</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1335.5</v>
+        <v>1333.6</v>
       </c>
       <c r="H16" t="n">
-        <v>1335.5</v>
+        <v>1333.6</v>
       </c>
       <c r="I16" t="n">
         <v>1321.3</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-06 12:30</t>
+          <t>2026-10-07 11:30</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2952.6</v>
+        <v>2947.6</v>
       </c>
       <c r="H18" t="n">
-        <v>2952.6</v>
+        <v>2947.6</v>
       </c>
       <c r="I18" t="n">
-        <v>2936.1</v>
+        <v>2928.9</v>
       </c>
     </row>
     <row r="19">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-06 09:45</t>
+          <t>2026-10-07 10:30</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1239,17 +1239,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-06 09:15</t>
+          <t>2026-10-07 14:15</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>77.14</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>77.14</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>76.06999999999999</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="23">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-06 15:00</t>
+          <t>2026-10-07 13:15</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>902.5</v>
+        <v>903.3</v>
       </c>
       <c r="H24" t="n">
-        <v>902.5</v>
+        <v>903.3</v>
       </c>
       <c r="I24" t="n">
-        <v>892.9</v>
+        <v>891.8</v>
       </c>
     </row>
     <row r="25">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1424,14 +1424,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-06 15:00</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1794.4</v>
+        <v>1794.7</v>
       </c>
       <c r="H27" t="n">
-        <v>1794.4</v>
+        <v>1794.7</v>
       </c>
       <c r="I27" t="n">
         <v>1769.1</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1461,17 +1461,276 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-06 09:30</t>
+          <t>2026-10-07 12:00</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4751.2</v>
+        <v>4728.1</v>
       </c>
       <c r="H28" t="n">
-        <v>4751.2</v>
+        <v>4728.1</v>
       </c>
       <c r="I28" t="n">
         <v>4702.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:00</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>355.05</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:00</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>352.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7910</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>7807.5</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:00</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>7917</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7917</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7807.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1194.9</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:15</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1189.9</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:30</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1196.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1196.2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1189.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>902.05</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>892.9</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:15</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>903.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>903.3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>891.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>945.8</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:00</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>945.7</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:00</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>948.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>948.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>945.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>936</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:15</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>935.35</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:15</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>945</v>
+      </c>
+      <c r="H34" t="n">
+        <v>945</v>
+      </c>
+      <c r="I34" t="n">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10612</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>10595</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:30</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>10630</v>
+      </c>
+      <c r="H35" t="n">
+        <v>10630</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10595</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -684,17 +684,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-07 14:30</t>
+          <t>2026-10-08 10:00</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1196.2</v>
+        <v>1195.3</v>
       </c>
       <c r="H7" t="n">
-        <v>1196.2</v>
+        <v>1195.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1189.9</v>
+        <v>1189.5</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +779,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -795,17 +795,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-07 10:45</t>
+          <t>2026-10-08 11:30</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1510.6</v>
+        <v>1511.9</v>
       </c>
       <c r="H10" t="n">
-        <v>1510.6</v>
+        <v>1511.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1493.6</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="11">
@@ -853,7 +853,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -869,14 +869,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-07 14:30</t>
+          <t>2026-10-08 11:30</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3931</v>
+        <v>3939.8</v>
       </c>
       <c r="H12" t="n">
-        <v>3931</v>
+        <v>3939.8</v>
       </c>
       <c r="I12" t="n">
         <v>3870.8</v>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1054,14 +1054,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-06 09:30</t>
+          <t>2026-10-08 10:30</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>168.85</v>
+        <v>168.69</v>
       </c>
       <c r="H17" t="n">
-        <v>168.85</v>
+        <v>168.69</v>
       </c>
       <c r="I17" t="n">
         <v>166.48</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-07 14:30</t>
+          <t>2026-10-08 10:00</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1196.2</v>
+        <v>1195.3</v>
       </c>
       <c r="H31" t="n">
-        <v>1196.2</v>
+        <v>1195.3</v>
       </c>
       <c r="I31" t="n">
-        <v>1189.9</v>
+        <v>1189.5</v>
       </c>
     </row>
     <row r="32">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1683,14 +1683,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-07 14:15</t>
+          <t>2026-10-08 10:00</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>945</v>
+        <v>939.25</v>
       </c>
       <c r="H34" t="n">
-        <v>945</v>
+        <v>939.25</v>
       </c>
       <c r="I34" t="n">
         <v>930</v>
@@ -1731,6 +1731,191 @@
       </c>
       <c r="I35" t="n">
         <v>10595</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:00</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1213.2</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1231.8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1231.8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1209.4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1702.1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1701</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:00</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1705.9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1705.9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>254.65</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:30</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>254.3</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>253.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1674.8</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:15</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1673.5</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:15</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1682.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1682.5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1658.6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1316.5</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1316.2</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:15</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1318.2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1318.2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1308.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -499,17 +499,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:00</t>
+          <t>2026-10-09 12:30</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7917</v>
+        <v>7939</v>
       </c>
       <c r="H2" t="n">
-        <v>7917</v>
+        <v>7939</v>
       </c>
       <c r="I2" t="n">
-        <v>7807.5</v>
+        <v>7608</v>
       </c>
     </row>
     <row r="3">
@@ -668,7 +668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -684,17 +684,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-08 10:00</t>
+          <t>2026-10-09 13:45</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1195.3</v>
+        <v>1198.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1195.3</v>
+        <v>1198.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1189.5</v>
+        <v>1167.4</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +779,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -795,14 +795,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-08 11:30</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1511.9</v>
+        <v>1519.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1511.9</v>
+        <v>1519.4</v>
       </c>
       <c r="I10" t="n">
         <v>1487</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-07 15:00</t>
+          <t>2026-10-09 12:30</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>7917</v>
+        <v>7939</v>
       </c>
       <c r="H13" t="n">
-        <v>7917</v>
+        <v>7939</v>
       </c>
       <c r="I13" t="n">
-        <v>7807.5</v>
+        <v>7608</v>
       </c>
     </row>
     <row r="14">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-07 10:30</t>
+          <t>2026-10-09 13:30</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>708.35</v>
+        <v>707.75</v>
       </c>
       <c r="H19" t="n">
-        <v>708.35</v>
+        <v>707.75</v>
       </c>
       <c r="I19" t="n">
-        <v>701</v>
+        <v>690.55</v>
       </c>
     </row>
     <row r="20">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1535,17 +1535,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-07 15:00</t>
+          <t>2026-10-09 12:30</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>7917</v>
+        <v>7939</v>
       </c>
       <c r="H30" t="n">
-        <v>7917</v>
+        <v>7939</v>
       </c>
       <c r="I30" t="n">
-        <v>7807.5</v>
+        <v>7608</v>
       </c>
     </row>
     <row r="31">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-08 10:00</t>
+          <t>2026-10-09 13:45</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1195.3</v>
+        <v>1198.6</v>
       </c>
       <c r="H31" t="n">
-        <v>1195.3</v>
+        <v>1198.6</v>
       </c>
       <c r="I31" t="n">
-        <v>1189.5</v>
+        <v>1167.4</v>
       </c>
     </row>
     <row r="32">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-07 14:00</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>948.5</v>
+        <v>948.45</v>
       </c>
       <c r="H33" t="n">
-        <v>948.5</v>
+        <v>948.45</v>
       </c>
       <c r="I33" t="n">
-        <v>945.7</v>
+        <v>937.55</v>
       </c>
     </row>
     <row r="34">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1683,17 +1683,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-08 10:00</t>
+          <t>2026-10-09 12:30</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>939.25</v>
+        <v>937.75</v>
       </c>
       <c r="H34" t="n">
-        <v>939.25</v>
+        <v>937.75</v>
       </c>
       <c r="I34" t="n">
-        <v>930</v>
+        <v>917.25</v>
       </c>
     </row>
     <row r="35">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1720,17 +1720,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-07 13:30</t>
+          <t>2026-10-09 13:15</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>10630</v>
+        <v>10618</v>
       </c>
       <c r="H35" t="n">
-        <v>10630</v>
+        <v>10618</v>
       </c>
       <c r="I35" t="n">
-        <v>10595</v>
+        <v>10426</v>
       </c>
     </row>
     <row r="36">
@@ -1916,6 +1916,672 @@
       </c>
       <c r="I40" t="n">
         <v>1308.7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>6660.5</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6578</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:45</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>6694.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6694.5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>6578</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1716</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:15</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1712</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1733.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1733.5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>7910</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>7807.5</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:30</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>7939</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7939</v>
+      </c>
+      <c r="I43" t="n">
+        <v>7608</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>854.2</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>842</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:45</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>859.15</v>
+      </c>
+      <c r="H44" t="n">
+        <v>859.15</v>
+      </c>
+      <c r="I44" t="n">
+        <v>840.15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1563.2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:15</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1546.6</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:00</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1572.3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1572.3</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1543.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4741</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:15</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4730.5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:00</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>4769</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4769</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4671.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1194.9</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:15</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1189.9</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:45</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1198.6</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1198.6</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1167.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6840</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:00</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6839</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>6850</v>
+      </c>
+      <c r="H48" t="n">
+        <v>6850</v>
+      </c>
+      <c r="I48" t="n">
+        <v>6767.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>706.25</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:15</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>705.6</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:30</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>707.75</v>
+      </c>
+      <c r="H49" t="n">
+        <v>707.75</v>
+      </c>
+      <c r="I49" t="n">
+        <v>690.55</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3655.9</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:15</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3655.5</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:30</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>3657.5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3657.5</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3607.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3936</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3927.9</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:30</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>3947.3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3947.3</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3908.4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>11305</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:15</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>11287</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:30</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>11315</v>
+      </c>
+      <c r="H52" t="n">
+        <v>11315</v>
+      </c>
+      <c r="I52" t="n">
+        <v>11225</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:45</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220.12</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:00</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>221.18</v>
+      </c>
+      <c r="H53" t="n">
+        <v>221.18</v>
+      </c>
+      <c r="I53" t="n">
+        <v>218.75</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1674.8</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:15</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1673.5</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:15</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1682.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1682.5</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1658.6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>945.8</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:00</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>945.7</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>948.45</v>
+      </c>
+      <c r="H55" t="n">
+        <v>948.45</v>
+      </c>
+      <c r="I55" t="n">
+        <v>937.55</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>936</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:15</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>935.35</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:30</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>937.75</v>
+      </c>
+      <c r="H56" t="n">
+        <v>937.75</v>
+      </c>
+      <c r="I56" t="n">
+        <v>917.25</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1510.5</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1508.4</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1519.4</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1519.4</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>10612</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>10595</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:15</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>10618</v>
+      </c>
+      <c r="H58" t="n">
+        <v>10618</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10426</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -536,14 +536,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-12 14:45</t>
+          <t>2026-10-13 09:30</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>403.95</v>
+        <v>404.9</v>
       </c>
       <c r="H3" t="n">
-        <v>403.95</v>
+        <v>404.9</v>
       </c>
       <c r="I3" t="n">
         <v>402.15</v>
@@ -552,44 +552,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>709.75</v>
+        <v>373.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-12 11:45</t>
+          <t>2026-10-12 15:00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>709.4</v>
+        <v>373</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-13 09:15</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>711.5</v>
+        <v>375.6</v>
       </c>
       <c r="H4" t="n">
-        <v>711.5</v>
+        <v>375.6</v>
       </c>
       <c r="I4" t="n">
-        <v>708.8</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -598,103 +598,843 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>308.45</v>
+        <v>709.75</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-12 10:30</t>
+          <t>2026-10-12 11:45</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308.05</v>
+        <v>709.4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-12 14:15</t>
+          <t>2026-10-12 15:15</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>308.7</v>
+        <v>711.5</v>
       </c>
       <c r="H5" t="n">
-        <v>308.7</v>
+        <v>711.5</v>
       </c>
       <c r="I5" t="n">
-        <v>305.85</v>
+        <v>708.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>441.05</v>
+        <v>4782.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-13 09:15</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>441</v>
+        <v>4758.4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-13 14:30</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>441.55</v>
+        <v>4792.5</v>
       </c>
       <c r="H6" t="n">
-        <v>441.55</v>
+        <v>4792.5</v>
       </c>
       <c r="I6" t="n">
-        <v>441</v>
+        <v>4749.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>308.45</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:30</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>308.05</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:30</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>305.85</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>441.05</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>441</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>441.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>441.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>440.55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C9" t="n">
         <v>1658.1</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2026-10-12 13:45</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E9" t="n">
         <v>1658</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-12 13:45</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G9" t="n">
         <v>1665.4</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H9" t="n">
         <v>1665.4</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I9" t="n">
         <v>1658</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1124.6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:15</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1124.4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1124.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1124.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1123.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>184.05</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:45</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>183.72</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:00</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>182.87</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>840.15</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>835</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:30</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>843.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>843.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>403.85</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:15</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>403.65</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:30</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>404.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>404.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>402.15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:00</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>373</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>375.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>375.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:45</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>166.11</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>166.53</v>
+      </c>
+      <c r="H15" t="n">
+        <v>166.53</v>
+      </c>
+      <c r="I15" t="n">
+        <v>165.87</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>886.5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:30</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>886.15</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:45</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>897.15</v>
+      </c>
+      <c r="H16" t="n">
+        <v>897.15</v>
+      </c>
+      <c r="I16" t="n">
+        <v>882.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1828</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:45</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1825.8</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1829.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1829.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1818.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>709.75</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:45</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>709.4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>711.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>711.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>708.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4782.2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4758.4</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:30</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>4792.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4792.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4749.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>857</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-10-12 09:15</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>855.85</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:30</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>861</v>
+      </c>
+      <c r="H20" t="n">
+        <v>861</v>
+      </c>
+      <c r="I20" t="n">
+        <v>846.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>125.22</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:30</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>125.48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>125.48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3607</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3593.2</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>3616.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3616.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3593.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>11225</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:00</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>11212</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:45</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>11233</v>
+      </c>
+      <c r="H23" t="n">
+        <v>11233</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11130</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>308.45</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:30</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>308.05</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:30</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>305.85</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>441.05</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>441</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>441.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>441.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>440.55</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1160.2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:30</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:15</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1161.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1161.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1152.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1486.2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-10-12 09:15</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1443.3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1506.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1506.7</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1443.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,14 +647,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:30</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4792.5</v>
+        <v>4789.9</v>
       </c>
       <c r="H6" t="n">
-        <v>4792.5</v>
+        <v>4789.9</v>
       </c>
       <c r="I6" t="n">
         <v>4749.6</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -758,17 +758,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-12 13:45</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1665.4</v>
+        <v>1658.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1665.4</v>
+        <v>1658.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="10">
@@ -964,7 +964,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -980,14 +980,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-13 11:45</t>
+          <t>2026-10-14 13:15</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>166.53</v>
+        <v>166.55</v>
       </c>
       <c r="H15" t="n">
-        <v>166.53</v>
+        <v>166.55</v>
       </c>
       <c r="I15" t="n">
         <v>165.87</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1017,14 +1017,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-14 15:00</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>897.15</v>
+        <v>887</v>
       </c>
       <c r="H16" t="n">
-        <v>897.15</v>
+        <v>887</v>
       </c>
       <c r="I16" t="n">
         <v>882.5</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-13 14:30</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4792.5</v>
+        <v>4789.9</v>
       </c>
       <c r="H19" t="n">
-        <v>4792.5</v>
+        <v>4789.9</v>
       </c>
       <c r="I19" t="n">
         <v>4749.6</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1202,14 +1202,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-13 13:30</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>125.48</v>
+        <v>125.67</v>
       </c>
       <c r="H21" t="n">
-        <v>125.48</v>
+        <v>125.67</v>
       </c>
       <c r="I21" t="n">
         <v>125</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1239,14 +1239,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-13 09:15</t>
+          <t>2026-10-14 13:15</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3616.6</v>
+        <v>3615</v>
       </c>
       <c r="H22" t="n">
-        <v>3616.6</v>
+        <v>3615</v>
       </c>
       <c r="I22" t="n">
         <v>3593.2</v>
@@ -1435,6 +1435,191 @@
       </c>
       <c r="I27" t="n">
         <v>1443.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:45</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>166.11</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:15</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>166.55</v>
+      </c>
+      <c r="H28" t="n">
+        <v>166.55</v>
+      </c>
+      <c r="I28" t="n">
+        <v>165.87</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>125.22</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>125.67</v>
+      </c>
+      <c r="H29" t="n">
+        <v>125.67</v>
+      </c>
+      <c r="I29" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>461</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:30</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>460.85</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:00</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>462.2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>462.2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>457.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3607</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3593.2</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:15</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>3615</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3615</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3593.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1745</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1743.2</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1754</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1754</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1743.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,17 +647,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-15 15:00</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4789.9</v>
+        <v>4794</v>
       </c>
       <c r="H6" t="n">
-        <v>4789.9</v>
+        <v>4794</v>
       </c>
       <c r="I6" t="n">
-        <v>4749.6</v>
+        <v>4679.7</v>
       </c>
     </row>
     <row r="7">
@@ -742,7 +742,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -758,17 +758,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
+          <t>2026-10-15 15:00</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1658.6</v>
+        <v>1666.3</v>
       </c>
       <c r="H9" t="n">
-        <v>1658.6</v>
+        <v>1666.3</v>
       </c>
       <c r="I9" t="n">
-        <v>1656</v>
+        <v>1634.8</v>
       </c>
     </row>
     <row r="10">
@@ -964,7 +964,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -980,14 +980,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-14 13:15</t>
+          <t>2026-10-15 09:45</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>166.55</v>
+        <v>166.84</v>
       </c>
       <c r="H15" t="n">
-        <v>166.55</v>
+        <v>166.84</v>
       </c>
       <c r="I15" t="n">
         <v>165.87</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00</t>
+          <t>2026-10-15 11:15</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>887</v>
+        <v>887.25</v>
       </c>
       <c r="H16" t="n">
-        <v>887</v>
+        <v>887.25</v>
       </c>
       <c r="I16" t="n">
-        <v>882.5</v>
+        <v>860.1</v>
       </c>
     </row>
     <row r="17">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-15 15:00</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4789.9</v>
+        <v>4794</v>
       </c>
       <c r="H19" t="n">
-        <v>4789.9</v>
+        <v>4794</v>
       </c>
       <c r="I19" t="n">
-        <v>4749.6</v>
+        <v>4679.7</v>
       </c>
     </row>
     <row r="20">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1239,14 +1239,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-14 13:15</t>
+          <t>2026-10-15 09:15</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3615</v>
+        <v>3625</v>
       </c>
       <c r="H22" t="n">
-        <v>3615</v>
+        <v>3625</v>
       </c>
       <c r="I22" t="n">
         <v>3593.2</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1276,14 +1276,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-13 14:45</t>
+          <t>2026-10-15 09:45</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>11233</v>
+        <v>11275</v>
       </c>
       <c r="H23" t="n">
-        <v>11233</v>
+        <v>11275</v>
       </c>
       <c r="I23" t="n">
         <v>11130</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1461,14 +1461,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-14 13:15</t>
+          <t>2026-10-15 09:45</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>166.55</v>
+        <v>166.84</v>
       </c>
       <c r="H28" t="n">
-        <v>166.55</v>
+        <v>166.84</v>
       </c>
       <c r="I28" t="n">
         <v>165.87</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-14 13:15</t>
+          <t>2026-10-15 09:15</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3615</v>
+        <v>3625</v>
       </c>
       <c r="H31" t="n">
-        <v>3615</v>
+        <v>3625</v>
       </c>
       <c r="I31" t="n">
         <v>3593.2</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1609,17 +1609,350 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>2026-10-15 09:30</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1748.8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1748.8</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1725.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:45</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>166.11</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:45</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>166.84</v>
+      </c>
+      <c r="H33" t="n">
+        <v>166.84</v>
+      </c>
+      <c r="I33" t="n">
+        <v>165.87</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>886.5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:30</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>886.15</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-15 11:15</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>887.25</v>
+      </c>
+      <c r="H34" t="n">
+        <v>887.25</v>
+      </c>
+      <c r="I34" t="n">
+        <v>860.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>446.05</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>445.9</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>446.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>446.8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>444.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1051.2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1041</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1064.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1064.9</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1038.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3607</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3593.2</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>3625</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3625</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3593.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>11225</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:00</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>11212</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:45</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>11275</v>
+      </c>
+      <c r="H38" t="n">
+        <v>11275</v>
+      </c>
+      <c r="I38" t="n">
+        <v>11130</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2559.6</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2550</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>2565</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2565</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1658.1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:45</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1658</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:00</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1666.3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1666.3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1634.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1745</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>2026-10-14 09:30</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>1754</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1754</v>
-      </c>
-      <c r="I32" t="n">
+      <c r="E41" t="n">
         <v>1743.2</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:30</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1748.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1748.8</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1725.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,14 +647,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00</t>
+          <t>2026-10-16 10:00</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4794</v>
+        <v>4782.7</v>
       </c>
       <c r="H6" t="n">
-        <v>4794</v>
+        <v>4782.7</v>
       </c>
       <c r="I6" t="n">
         <v>4679.7</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -758,14 +758,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00</t>
+          <t>2026-10-16 15:00</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1666.3</v>
+        <v>1664.7</v>
       </c>
       <c r="H9" t="n">
-        <v>1666.3</v>
+        <v>1664.7</v>
       </c>
       <c r="I9" t="n">
         <v>1634.8</v>
@@ -853,7 +853,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -869,17 +869,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-13 13:30</t>
+          <t>2026-10-16 13:00</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>843.3</v>
+        <v>843.85</v>
       </c>
       <c r="H12" t="n">
-        <v>843.3</v>
+        <v>843.85</v>
       </c>
       <c r="I12" t="n">
-        <v>835</v>
+        <v>808.75</v>
       </c>
     </row>
     <row r="13">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00</t>
+          <t>2026-10-16 10:00</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4794</v>
+        <v>4782.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4794</v>
+        <v>4782.7</v>
       </c>
       <c r="I19" t="n">
         <v>4679.7</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1609,14 +1609,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-16 09:45</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1748.8</v>
+        <v>1759.1</v>
       </c>
       <c r="H32" t="n">
-        <v>1748.8</v>
+        <v>1759.1</v>
       </c>
       <c r="I32" t="n">
         <v>1725.5</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1720,17 +1720,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-15 09:15</t>
+          <t>2026-10-16 13:30</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>446.8</v>
+        <v>446.2</v>
       </c>
       <c r="H35" t="n">
-        <v>446.8</v>
+        <v>446.2</v>
       </c>
       <c r="I35" t="n">
-        <v>444.1</v>
+        <v>435.65</v>
       </c>
     </row>
     <row r="36">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1757,14 +1757,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-16 09:30</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1064.9</v>
+        <v>1053.4</v>
       </c>
       <c r="H36" t="n">
-        <v>1064.9</v>
+        <v>1053.4</v>
       </c>
       <c r="I36" t="n">
         <v>1038.1</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1905,14 +1905,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00</t>
+          <t>2026-10-16 15:00</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1666.3</v>
+        <v>1664.7</v>
       </c>
       <c r="H40" t="n">
-        <v>1666.3</v>
+        <v>1664.7</v>
       </c>
       <c r="I40" t="n">
         <v>1634.8</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1942,17 +1942,276 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-16 09:45</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1748.8</v>
+        <v>1759.1</v>
       </c>
       <c r="H41" t="n">
-        <v>1748.8</v>
+        <v>1759.1</v>
       </c>
       <c r="I41" t="n">
         <v>1725.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>230.18</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:00</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:00</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>230.3</v>
+      </c>
+      <c r="H42" t="n">
+        <v>230.3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>225.22</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>840.15</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>835</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:00</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>843.85</v>
+      </c>
+      <c r="H43" t="n">
+        <v>843.85</v>
+      </c>
+      <c r="I43" t="n">
+        <v>808.75</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>9113.5</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:00</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>9060</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:45</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>9156</v>
+      </c>
+      <c r="H44" t="n">
+        <v>9156</v>
+      </c>
+      <c r="I44" t="n">
+        <v>8937.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2853.5</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:30</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2843.4</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:30</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>2861.8</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2861.8</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2843.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1051.2</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1041</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:30</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1053.4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1053.4</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1038.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1745</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1743.2</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:45</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1759.1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1759.1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1725.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>426.3</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:00</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>424.5</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:45</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>427</v>
+      </c>
+      <c r="H48" t="n">
+        <v>427</v>
+      </c>
+      <c r="I48" t="n">
+        <v>424.05</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -536,17 +536,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-19 13:15</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2318.8</v>
+        <v>2319.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2318.8</v>
+        <v>2319.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2310</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="4">
@@ -631,7 +631,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,17 +647,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-21 10:30</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>436.9</v>
+        <v>435.95</v>
       </c>
       <c r="H6" t="n">
-        <v>436.9</v>
+        <v>435.95</v>
       </c>
       <c r="I6" t="n">
-        <v>435.05</v>
+        <v>434.75</v>
       </c>
     </row>
     <row r="7">
@@ -668,7 +668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -684,17 +684,757 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-19 14:45</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4551.1</v>
+        <v>4553.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4551.1</v>
+        <v>4553.8</v>
       </c>
       <c r="I7" t="n">
+        <v>4474.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1255.4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1248.2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1256</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1256</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1245.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1725.1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1724.5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1729</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1729</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1724.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2317.8</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:15</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2310</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2319.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2319.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:00</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>368.55</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>366.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:30</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>372.2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>372.95</v>
+      </c>
+      <c r="H12" t="n">
+        <v>372.95</v>
+      </c>
+      <c r="I12" t="n">
+        <v>371.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>165.87</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>165.67</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>164.88</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>700.35</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:00</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>700.15</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>701</v>
+      </c>
+      <c r="H14" t="n">
+        <v>701</v>
+      </c>
+      <c r="I14" t="n">
+        <v>698.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>532.6</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:45</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>531.7</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>533.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>533.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>531.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1631</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:15</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1627.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1632.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1632.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1626.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4615</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:30</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4608</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>4620</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4620</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4585</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>845.7</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:15</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>841</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>848.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>848.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>831.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>437.2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:15</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>436.9</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:45</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:15</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:30</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="H20" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="I20" t="n">
+        <v>70.61</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1462</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1460.3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1462.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1462.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1460.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>300</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:15</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>301.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>301.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>299.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1725.5</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1723.5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:30</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1730</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1730</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1721.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>171.66</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:30</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>171.19</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>172.45</v>
+      </c>
+      <c r="H24" t="n">
+        <v>172.45</v>
+      </c>
+      <c r="I24" t="n">
+        <v>170.66</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4361</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:00</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4360.5</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>4365</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4365</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4351.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4550.4</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:15</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
         <v>4533.8</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>4553.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4553.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4474.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1107.3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1112.9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1112.9</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1106</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -684,14 +684,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-22 09:45</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4553.8</v>
+        <v>4563.7</v>
       </c>
       <c r="H7" t="n">
-        <v>4553.8</v>
+        <v>4563.7</v>
       </c>
       <c r="I7" t="n">
         <v>4474.6</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 12:45</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -731,7 +731,7 @@
         <v>1256</v>
       </c>
       <c r="I8" t="n">
-        <v>1245.6</v>
+        <v>1214.1</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -758,17 +758,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 10:00</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1729</v>
+        <v>1738.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1729</v>
+        <v>1738.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1724.5</v>
+        <v>1715.3</v>
       </c>
     </row>
     <row r="10">
@@ -853,7 +853,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -869,17 +869,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 11:00</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>372.95</v>
+        <v>373.6</v>
       </c>
       <c r="H12" t="n">
-        <v>372.95</v>
+        <v>373.6</v>
       </c>
       <c r="I12" t="n">
-        <v>371.75</v>
+        <v>368.5</v>
       </c>
     </row>
     <row r="13">
@@ -890,7 +890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -906,14 +906,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 13:30</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>166.6</v>
+        <v>166.29</v>
       </c>
       <c r="H13" t="n">
-        <v>166.6</v>
+        <v>166.29</v>
       </c>
       <c r="I13" t="n">
         <v>164.88</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -943,17 +943,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 10:45</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>701</v>
+        <v>702.1</v>
       </c>
       <c r="H14" t="n">
-        <v>701</v>
+        <v>702.1</v>
       </c>
       <c r="I14" t="n">
-        <v>698.5</v>
+        <v>691.65</v>
       </c>
     </row>
     <row r="15">
@@ -964,7 +964,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -980,17 +980,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 11:15</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>533.3</v>
+        <v>532.75</v>
       </c>
       <c r="H15" t="n">
-        <v>533.3</v>
+        <v>532.75</v>
       </c>
       <c r="I15" t="n">
-        <v>531.7</v>
+        <v>528.9</v>
       </c>
     </row>
     <row r="16">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 13:45</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1632.7</v>
+        <v>1636.2</v>
       </c>
       <c r="H16" t="n">
-        <v>1632.7</v>
+        <v>1636.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1626.4</v>
+        <v>1616.6</v>
       </c>
     </row>
     <row r="17">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 10:45</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4620</v>
+        <v>4616.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4620</v>
+        <v>4616.3</v>
       </c>
       <c r="I17" t="n">
-        <v>4585</v>
+        <v>4548.9</v>
       </c>
     </row>
     <row r="18">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 14:30</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>848.4</v>
+        <v>848.55</v>
       </c>
       <c r="H18" t="n">
-        <v>848.4</v>
+        <v>848.55</v>
       </c>
       <c r="I18" t="n">
         <v>831.25</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-21 12:45</t>
+          <t>2026-10-22 14:30</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>437.3</v>
+        <v>438.1</v>
       </c>
       <c r="H19" t="n">
-        <v>437.3</v>
+        <v>438.1</v>
       </c>
       <c r="I19" t="n">
-        <v>436</v>
+        <v>433.75</v>
       </c>
     </row>
     <row r="20">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 11:45</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1462.3</v>
+        <v>1466.8</v>
       </c>
       <c r="H21" t="n">
-        <v>1462.3</v>
+        <v>1466.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1460.3</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="22">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1239,202 +1239,1090 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 14:00</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>301.6</v>
+        <v>300.65</v>
       </c>
       <c r="H22" t="n">
-        <v>301.6</v>
+        <v>300.65</v>
       </c>
       <c r="I22" t="n">
-        <v>299.1</v>
+        <v>295.55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1725.5</v>
+        <v>1634.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1723.5</v>
+        <v>1628.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-21 14:30</t>
+          <t>2026-10-22 14:15</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1730</v>
+        <v>1635.7</v>
       </c>
       <c r="H23" t="n">
-        <v>1730</v>
+        <v>1635.7</v>
       </c>
       <c r="I23" t="n">
-        <v>1721.7</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>171.66</v>
+        <v>1725.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-21 13:30</t>
+          <t>2026-10-21 12:15</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>171.19</v>
+        <v>1723.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-22 09:30</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>172.45</v>
+        <v>1736.8</v>
       </c>
       <c r="H24" t="n">
-        <v>172.45</v>
+        <v>1736.8</v>
       </c>
       <c r="I24" t="n">
-        <v>170.66</v>
+        <v>1719.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4361</v>
+        <v>171.66</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-21 12:00</t>
+          <t>2026-10-21 13:30</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4360.5</v>
+        <v>171.19</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 15:15</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4365</v>
+        <v>172.33</v>
       </c>
       <c r="H25" t="n">
-        <v>4365</v>
+        <v>172.33</v>
       </c>
       <c r="I25" t="n">
-        <v>4351.1</v>
+        <v>168.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4550.4</v>
+        <v>4361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-19 09:15</t>
+          <t>2026-10-21 12:00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4533.8</v>
+        <v>4360.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-22 11:15</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4553.8</v>
+        <v>4368.5</v>
       </c>
       <c r="H26" t="n">
-        <v>4553.8</v>
+        <v>4368.5</v>
       </c>
       <c r="I26" t="n">
-        <v>4474.6</v>
+        <v>4329.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4550.4</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:15</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4533.8</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:45</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>4563.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4563.7</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4474.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>1107.3</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2026-10-21 14:45</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E28" t="n">
         <v>1106</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1116</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1116</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1100.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1725.1</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>2026-10-21 14:45</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>1112.9</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1112.9</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="E29" t="n">
+        <v>1724.5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1738.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1738.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1715.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>283.25</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>282.3</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>283.65</v>
+      </c>
+      <c r="H30" t="n">
+        <v>283.65</v>
+      </c>
+      <c r="I30" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>808.55</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>808.4</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>819.3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>819.3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>808.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1300.2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1296.7</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1306.6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1306.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1296.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:15</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>402.55</v>
+      </c>
+      <c r="H33" t="n">
+        <v>402.55</v>
+      </c>
+      <c r="I33" t="n">
+        <v>395.75</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>165.87</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>165.67</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:30</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>166.29</v>
+      </c>
+      <c r="H34" t="n">
+        <v>166.29</v>
+      </c>
+      <c r="I34" t="n">
+        <v>164.88</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2843.4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2828.2</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>2849.4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2849.4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2828.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1814.4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:45</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1811.3</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:00</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1817.6</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1817.6</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1810.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1631</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:15</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1627.1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:45</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1636.2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1636.2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1616.6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>845.7</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:15</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>841</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:30</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>848.55</v>
+      </c>
+      <c r="H38" t="n">
+        <v>848.55</v>
+      </c>
+      <c r="I38" t="n">
+        <v>831.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>256.95</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>256.45</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>257.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>257.3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>256.45</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1003.5</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1003</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1007.8</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1007.8</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1001.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>11125</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>10990</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:30</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>11135</v>
+      </c>
+      <c r="H41" t="n">
+        <v>11135</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10990</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>152.77</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>152.61</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:30</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>153.14</v>
+      </c>
+      <c r="H42" t="n">
+        <v>153.14</v>
+      </c>
+      <c r="I42" t="n">
+        <v>152.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1462</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1460.3</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:45</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1466.8</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1466.8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>245</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>246.15</v>
+      </c>
+      <c r="H44" t="n">
+        <v>246.15</v>
+      </c>
+      <c r="I44" t="n">
+        <v>244.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>300</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:15</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:00</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>300.65</v>
+      </c>
+      <c r="H45" t="n">
+        <v>300.65</v>
+      </c>
+      <c r="I45" t="n">
+        <v>295.55</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1634.5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1628.6</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:15</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1635.7</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1635.7</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1725.5</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1723.5</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1736.8</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1736.8</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1719.6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>953.2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>949.5</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:45</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>953.45</v>
+      </c>
+      <c r="H48" t="n">
+        <v>953.45</v>
+      </c>
+      <c r="I48" t="n">
+        <v>949.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>171.66</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:30</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>171.19</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:15</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>172.33</v>
+      </c>
+      <c r="H49" t="n">
+        <v>172.33</v>
+      </c>
+      <c r="I49" t="n">
+        <v>168.11</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4550.4</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:15</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4533.8</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:45</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>4563.7</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4563.7</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4474.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1107.3</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
         <v>1106</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1116</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1116</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1100.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -499,17 +499,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-23 14:30</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7695</v>
+        <v>7708.5</v>
       </c>
       <c r="H2" t="n">
-        <v>7695</v>
+        <v>7708.5</v>
       </c>
       <c r="I2" t="n">
-        <v>7677</v>
+        <v>7468</v>
       </c>
     </row>
     <row r="3">
@@ -742,7 +742,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -758,14 +758,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1738.2</v>
+        <v>1727.7</v>
       </c>
       <c r="H9" t="n">
-        <v>1738.2</v>
+        <v>1727.7</v>
       </c>
       <c r="I9" t="n">
         <v>1715.3</v>
@@ -1005,26 +1005,26 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1631</v>
+        <v>1624.01</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1627.1</v>
+        <v>1616.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-22 13:45</t>
+          <t>2026-10-22 09:45</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1636.2</v>
+        <v>1628</v>
       </c>
       <c r="H16" t="n">
-        <v>1636.2</v>
+        <v>1628</v>
       </c>
       <c r="I16" t="n">
         <v>1616.6</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1165,14 +1165,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-21 11:30</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>71.63</v>
+        <v>71.48</v>
       </c>
       <c r="H20" t="n">
-        <v>71.63</v>
+        <v>71.48</v>
       </c>
       <c r="I20" t="n">
         <v>70.61</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1202,14 +1202,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-22 11:45</t>
+          <t>2026-10-23 13:00</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1466.8</v>
+        <v>1462.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1466.8</v>
+        <v>1462.4</v>
       </c>
       <c r="I21" t="n">
         <v>1451</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-22 14:15</t>
+          <t>2026-10-23 15:00</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1635.7</v>
+        <v>1637.6</v>
       </c>
       <c r="H23" t="n">
-        <v>1635.7</v>
+        <v>1637.6</v>
       </c>
       <c r="I23" t="n">
-        <v>1620</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="24">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1498,14 +1498,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1738.2</v>
+        <v>1727.7</v>
       </c>
       <c r="H29" t="n">
-        <v>1738.2</v>
+        <v>1727.7</v>
       </c>
       <c r="I29" t="n">
         <v>1715.3</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-23 15:00</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>819.3</v>
+        <v>809.8</v>
       </c>
       <c r="H31" t="n">
-        <v>819.3</v>
+        <v>809.8</v>
       </c>
       <c r="I31" t="n">
-        <v>808.4</v>
+        <v>772.5</v>
       </c>
     </row>
     <row r="32">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-22 15:00</t>
+          <t>2026-10-23 15:15</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1817.6</v>
+        <v>1814.7</v>
       </c>
       <c r="H36" t="n">
-        <v>1817.6</v>
+        <v>1814.7</v>
       </c>
       <c r="I36" t="n">
-        <v>1810.6</v>
+        <v>1781.1</v>
       </c>
     </row>
     <row r="37">
@@ -1782,26 +1782,26 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1631</v>
+        <v>1624.01</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1627.1</v>
+        <v>1616.6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-22 13:45</t>
+          <t>2026-10-22 09:45</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1636.2</v>
+        <v>1628</v>
       </c>
       <c r="H37" t="n">
-        <v>1636.2</v>
+        <v>1628</v>
       </c>
       <c r="I37" t="n">
         <v>1616.6</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1868,17 +1868,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-22 12:00</t>
+          <t>2026-10-23 15:00</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>257.3</v>
+        <v>257</v>
       </c>
       <c r="H39" t="n">
-        <v>257.3</v>
+        <v>257</v>
       </c>
       <c r="I39" t="n">
-        <v>256.45</v>
+        <v>254.85</v>
       </c>
     </row>
     <row r="40">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1942,14 +1942,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-22 14:30</t>
+          <t>2026-10-23 13:45</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>11135</v>
+        <v>11168</v>
       </c>
       <c r="H41" t="n">
-        <v>11135</v>
+        <v>11168</v>
       </c>
       <c r="I41" t="n">
         <v>10990</v>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2016,14 +2016,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-22 11:45</t>
+          <t>2026-10-23 13:00</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1466.8</v>
+        <v>1462.4</v>
       </c>
       <c r="H43" t="n">
-        <v>1466.8</v>
+        <v>1462.4</v>
       </c>
       <c r="I43" t="n">
         <v>1451</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2053,17 +2053,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-23 14:45</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>246.15</v>
+        <v>245.35</v>
       </c>
       <c r="H44" t="n">
-        <v>246.15</v>
+        <v>245.35</v>
       </c>
       <c r="I44" t="n">
-        <v>244.8</v>
+        <v>242.3</v>
       </c>
     </row>
     <row r="45">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2127,17 +2127,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-22 14:15</t>
+          <t>2026-10-23 15:00</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1635.7</v>
+        <v>1637.6</v>
       </c>
       <c r="H46" t="n">
-        <v>1635.7</v>
+        <v>1637.6</v>
       </c>
       <c r="I46" t="n">
-        <v>1620</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="47">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-22 14:45</t>
+          <t>2026-10-23 15:15</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>953.45</v>
+        <v>963.9</v>
       </c>
       <c r="H48" t="n">
-        <v>953.45</v>
+        <v>963.9</v>
       </c>
       <c r="I48" t="n">
-        <v>949.5</v>
+        <v>948.9</v>
       </c>
     </row>
     <row r="49">
@@ -2323,6 +2323,561 @@
       </c>
       <c r="I51" t="n">
         <v>1100.3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>7688</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-10-19 15:00</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>7677</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:30</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>7708.5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7708.5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>7468</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>808.55</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>808.4</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:00</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>809.8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>809.8</v>
+      </c>
+      <c r="I53" t="n">
+        <v>772.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>8937.5</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:30</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>8926</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:15</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>8950</v>
+      </c>
+      <c r="H54" t="n">
+        <v>8950</v>
+      </c>
+      <c r="I54" t="n">
+        <v>8797.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7008.5</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6993.5</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:00</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>7020</v>
+      </c>
+      <c r="H55" t="n">
+        <v>7020</v>
+      </c>
+      <c r="I55" t="n">
+        <v>6918</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>840.5</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:45</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>838.15</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:15</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>841.55</v>
+      </c>
+      <c r="H56" t="n">
+        <v>841.55</v>
+      </c>
+      <c r="I56" t="n">
+        <v>837.3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>857.15</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:00</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>853.45</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:15</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>860.3</v>
+      </c>
+      <c r="H57" t="n">
+        <v>860.3</v>
+      </c>
+      <c r="I57" t="n">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1814.4</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:45</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1811.3</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:15</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1814.7</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1814.7</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1781.1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>256.95</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>256.45</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:00</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>257</v>
+      </c>
+      <c r="H59" t="n">
+        <v>257</v>
+      </c>
+      <c r="I59" t="n">
+        <v>254.85</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>11125</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>10990</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:45</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>11168</v>
+      </c>
+      <c r="H60" t="n">
+        <v>11168</v>
+      </c>
+      <c r="I60" t="n">
+        <v>10990</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1462</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1460.3</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:00</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1462.4</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1462.4</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>245</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:45</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>245.35</v>
+      </c>
+      <c r="H62" t="n">
+        <v>245.35</v>
+      </c>
+      <c r="I62" t="n">
+        <v>242.3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1634.5</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1628.6</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:00</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1637.6</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1637.6</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1636.2</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:45</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1626.9</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:15</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1643</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1643</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1605.1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>953.2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>949.5</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:15</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>963.9</v>
+      </c>
+      <c r="H65" t="n">
+        <v>963.9</v>
+      </c>
+      <c r="I65" t="n">
+        <v>948.9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>340.7</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:45</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:45</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>342.15</v>
+      </c>
+      <c r="H66" t="n">
+        <v>342.15</v>
+      </c>
+      <c r="I66" t="n">
+        <v>340.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -536,17 +536,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-26 09:45</t>
+          <t>2026-10-27 14:30</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2484.2</v>
+        <v>2471.7</v>
       </c>
       <c r="H3" t="n">
-        <v>2484.2</v>
+        <v>2471.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2447.8</v>
+        <v>2433.4</v>
       </c>
     </row>
     <row r="4">
@@ -779,7 +779,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -795,17 +795,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-26 15:00</t>
+          <t>2026-10-27 11:45</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>687.2</v>
+        <v>688.1</v>
       </c>
       <c r="H10" t="n">
-        <v>687.2</v>
+        <v>688.1</v>
       </c>
       <c r="I10" t="n">
-        <v>684</v>
+        <v>683.85</v>
       </c>
     </row>
     <row r="11">
@@ -890,7 +890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 15:15</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>74.45</v>
+        <v>74.56</v>
       </c>
       <c r="H13" t="n">
-        <v>74.45</v>
+        <v>74.56</v>
       </c>
       <c r="I13" t="n">
-        <v>73.22</v>
+        <v>73.19</v>
       </c>
     </row>
     <row r="14">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1202,14 +1202,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 11:15</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>313.9</v>
+        <v>314.45</v>
       </c>
       <c r="H21" t="n">
-        <v>313.9</v>
+        <v>314.45</v>
       </c>
       <c r="I21" t="n">
         <v>310.5</v>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1313,14 +1313,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-26 11:30</t>
+          <t>2026-10-27 14:30</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>952.25</v>
+        <v>951.2</v>
       </c>
       <c r="H24" t="n">
-        <v>952.25</v>
+        <v>951.2</v>
       </c>
       <c r="I24" t="n">
         <v>943.5</v>
@@ -1472,6 +1472,413 @@
       </c>
       <c r="I28" t="n">
         <v>1094</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1134.6</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:45</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1118.1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1164.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1164.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1118.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2462.1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2451</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:30</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>2471.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2471.7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2433.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10834</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:15</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>10810</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>10901</v>
+      </c>
+      <c r="H31" t="n">
+        <v>10901</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10735</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1415</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:15</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1451.9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1451.9</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>356.05</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:15</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>358</v>
+      </c>
+      <c r="H33" t="n">
+        <v>358</v>
+      </c>
+      <c r="I33" t="n">
+        <v>354.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1002.8</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1002.2</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:45</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1005</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1005</v>
+      </c>
+      <c r="I34" t="n">
+        <v>999.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1781.1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1777.1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:15</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1783.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1783.6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1758.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>437.45</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>437</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>451.2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>451.2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>73.76000000000001</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>73.22</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="H37" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="I37" t="n">
+        <v>73.19</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>312.75</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-27 11:15</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>314.45</v>
+      </c>
+      <c r="H38" t="n">
+        <v>314.45</v>
+      </c>
+      <c r="I38" t="n">
+        <v>310.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1227</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:45</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1240.7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1240.7</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1227</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -536,14 +536,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30</t>
+          <t>2026-10-28 12:30</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2471.7</v>
+        <v>2476</v>
       </c>
       <c r="H3" t="n">
-        <v>2471.7</v>
+        <v>2476</v>
       </c>
       <c r="I3" t="n">
         <v>2433.4</v>
@@ -557,7 +557,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -573,14 +573,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-26 09:45</t>
+          <t>2026-10-28 11:15</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2263.8</v>
+        <v>2263.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2263.8</v>
+        <v>2263.9</v>
       </c>
       <c r="I4" t="n">
         <v>2234.3</v>
@@ -594,7 +594,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -610,17 +610,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 11:45</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>912.2</v>
+        <v>908.25</v>
       </c>
       <c r="H5" t="n">
-        <v>912.2</v>
+        <v>908.25</v>
       </c>
       <c r="I5" t="n">
-        <v>906.55</v>
+        <v>900.05</v>
       </c>
     </row>
     <row r="6">
@@ -668,7 +668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -684,17 +684,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 09:45</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4540.1</v>
+        <v>4526.6</v>
       </c>
       <c r="H7" t="n">
-        <v>4540.1</v>
+        <v>4526.6</v>
       </c>
       <c r="I7" t="n">
-        <v>4507.9</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="8">
@@ -890,7 +890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -906,14 +906,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15</t>
+          <t>2026-10-28 09:45</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>74.56</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>74.56</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>73.19</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -943,17 +943,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-28 11:15</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>256.25</v>
+        <v>255.1</v>
       </c>
       <c r="H14" t="n">
-        <v>256.25</v>
+        <v>255.1</v>
       </c>
       <c r="I14" t="n">
-        <v>254.5</v>
+        <v>252.85</v>
       </c>
     </row>
     <row r="15">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 14:15</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1188.2</v>
+        <v>1179.2</v>
       </c>
       <c r="H18" t="n">
-        <v>1188.2</v>
+        <v>1179.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1169.8</v>
+        <v>1139.2</v>
       </c>
     </row>
     <row r="19">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1202,14 +1202,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-27 11:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>314.45</v>
+        <v>314.8</v>
       </c>
       <c r="H21" t="n">
-        <v>314.45</v>
+        <v>314.8</v>
       </c>
       <c r="I21" t="n">
         <v>310.5</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 15:00</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>291.8</v>
+        <v>291</v>
       </c>
       <c r="H23" t="n">
-        <v>291.8</v>
+        <v>291</v>
       </c>
       <c r="I23" t="n">
-        <v>289.5</v>
+        <v>283.7</v>
       </c>
     </row>
     <row r="24">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1313,14 +1313,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>951.2</v>
+        <v>951.65</v>
       </c>
       <c r="H24" t="n">
-        <v>951.2</v>
+        <v>951.65</v>
       </c>
       <c r="I24" t="n">
         <v>943.5</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1498,14 +1498,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-27 15:00</t>
+          <t>2026-10-28 14:15</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1164.1</v>
+        <v>1137.8</v>
       </c>
       <c r="H29" t="n">
-        <v>1164.1</v>
+        <v>1137.8</v>
       </c>
       <c r="I29" t="n">
         <v>1118.1</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1535,14 +1535,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30</t>
+          <t>2026-10-28 12:30</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2471.7</v>
+        <v>2476</v>
       </c>
       <c r="H30" t="n">
-        <v>2471.7</v>
+        <v>2476</v>
       </c>
       <c r="I30" t="n">
         <v>2433.4</v>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1683,14 +1683,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="H34" t="n">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="I34" t="n">
         <v>999.7</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1720,14 +1720,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-27 14:15</t>
+          <t>2026-10-28 11:30</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1783.6</v>
+        <v>1785.9</v>
       </c>
       <c r="H35" t="n">
-        <v>1783.6</v>
+        <v>1785.9</v>
       </c>
       <c r="I35" t="n">
         <v>1758.2</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1794,14 +1794,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15</t>
+          <t>2026-10-28 09:45</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>74.56</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>74.56</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="I37" t="n">
         <v>73.19</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1831,14 +1831,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-27 11:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>314.45</v>
+        <v>314.8</v>
       </c>
       <c r="H38" t="n">
-        <v>314.45</v>
+        <v>314.8</v>
       </c>
       <c r="I38" t="n">
         <v>310.5</v>
@@ -1879,6 +1879,820 @@
       </c>
       <c r="I39" t="n">
         <v>1227</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1134.6</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:45</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1118.1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:15</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1137.8</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1137.8</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1118.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2462.1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2451</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:30</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>2476</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2476</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2433.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2260</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2252.3</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:15</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>2263.9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2263.9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2234.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1635</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:15</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1628.3</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:30</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1637.4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1637.4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1628.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>907.4</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>906.55</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:45</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>908.25</v>
+      </c>
+      <c r="H44" t="n">
+        <v>908.25</v>
+      </c>
+      <c r="I44" t="n">
+        <v>900.05</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4515</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4507.9</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:45</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>4526.6</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4526.6</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>356.05</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:15</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>358</v>
+      </c>
+      <c r="H46" t="n">
+        <v>358</v>
+      </c>
+      <c r="I46" t="n">
+        <v>354.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1002.8</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1002.2</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1012</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1012</v>
+      </c>
+      <c r="I47" t="n">
+        <v>999.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>510.4</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:00</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>512.45</v>
+      </c>
+      <c r="H48" t="n">
+        <v>512.45</v>
+      </c>
+      <c r="I48" t="n">
+        <v>508.4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1781.1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1777.1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:30</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1785.9</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1785.9</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1758.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1375.1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1361.4</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:15</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1377.6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1377.6</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1361.4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1578.4</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:30</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1582.2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1582.2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1556.1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>73.76000000000001</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>73.22</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:45</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>74.06999999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>74.06999999999999</v>
+      </c>
+      <c r="I52" t="n">
+        <v>73.19</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>254.8</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:15</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>255.1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>255.1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>252.85</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4100</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4040.1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:15</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>4104</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4104</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3930.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1177.6</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1169.8</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:15</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1179.2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1179.2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1139.2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1156.2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1149.8</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:45</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1159.6</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1159.6</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>312.75</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>314.8</v>
+      </c>
+      <c r="H57" t="n">
+        <v>314.8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>310.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>949.95</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>945.2</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>951.65</v>
+      </c>
+      <c r="H58" t="n">
+        <v>951.65</v>
+      </c>
+      <c r="I58" t="n">
+        <v>943.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:15</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>259.3</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:30</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>260</v>
+      </c>
+      <c r="H59" t="n">
+        <v>260</v>
+      </c>
+      <c r="I59" t="n">
+        <v>259.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2432.1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2414</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:00</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>2436.3</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2436.3</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2408.2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1738.33</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1734.9</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1750</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1750</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1734.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,7 +557,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -573,17 +573,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-28 11:15</t>
+          <t>2026-10-29 14:30</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2263.9</v>
+        <v>2282.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2263.9</v>
+        <v>2282.5</v>
       </c>
       <c r="I4" t="n">
-        <v>2234.3</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="5">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-28 14:15</t>
+          <t>2026-10-29 10:15</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1179.2</v>
+        <v>1183.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1179.2</v>
+        <v>1183.6</v>
       </c>
       <c r="I18" t="n">
         <v>1139.2</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1979,17 +1979,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-28 11:15</t>
+          <t>2026-10-29 14:30</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2263.9</v>
+        <v>2282.5</v>
       </c>
       <c r="H42" t="n">
-        <v>2263.9</v>
+        <v>2282.5</v>
       </c>
       <c r="I42" t="n">
-        <v>2234.3</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="43">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2201,14 +2201,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-28 11:00</t>
+          <t>2026-10-29 09:45</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>512.45</v>
+        <v>512.9</v>
       </c>
       <c r="H48" t="n">
-        <v>512.45</v>
+        <v>512.9</v>
       </c>
       <c r="I48" t="n">
         <v>508.4</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2275,14 +2275,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-28 13:15</t>
+          <t>2026-10-29 11:00</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1377.6</v>
+        <v>1375.7</v>
       </c>
       <c r="H50" t="n">
-        <v>1377.6</v>
+        <v>1375.7</v>
       </c>
       <c r="I50" t="n">
         <v>1361.4</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2423,14 +2423,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-28 15:15</t>
+          <t>2026-10-29 15:00</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>4104</v>
+        <v>4105</v>
       </c>
       <c r="H54" t="n">
-        <v>4104</v>
+        <v>4105</v>
       </c>
       <c r="I54" t="n">
         <v>3930.5</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2460,14 +2460,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-28 14:15</t>
+          <t>2026-10-29 10:15</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1179.2</v>
+        <v>1183.6</v>
       </c>
       <c r="H55" t="n">
-        <v>1179.2</v>
+        <v>1183.6</v>
       </c>
       <c r="I55" t="n">
         <v>1139.2</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-28 10:45</t>
+          <t>2026-10-29 09:45</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1159.6</v>
+        <v>1160.4</v>
       </c>
       <c r="H56" t="n">
-        <v>1159.6</v>
+        <v>1160.4</v>
       </c>
       <c r="I56" t="n">
         <v>1148</v>
@@ -2693,6 +2693,413 @@
       </c>
       <c r="I61" t="n">
         <v>1734.9</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1134.6</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:45</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1118.1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:15</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1137.8</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1137.8</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1118.1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2260</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2252.3</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:30</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>2282.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2282.5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:00</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:30</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>392.35</v>
+      </c>
+      <c r="H64" t="n">
+        <v>392.35</v>
+      </c>
+      <c r="I64" t="n">
+        <v>388.7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>510.4</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:45</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>512.9</v>
+      </c>
+      <c r="H65" t="n">
+        <v>512.9</v>
+      </c>
+      <c r="I65" t="n">
+        <v>508.4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1375.1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1361.4</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:00</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1375.7</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1375.7</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1361.4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1156.2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1149.8</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:45</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1160.4</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1160.4</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>290.65</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:00</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>291</v>
+      </c>
+      <c r="H68" t="n">
+        <v>291</v>
+      </c>
+      <c r="I68" t="n">
+        <v>283.7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1163.1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:15</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1162</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1169</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1169</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1156.2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>827.09</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>810.2</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>832.4</v>
+      </c>
+      <c r="H70" t="n">
+        <v>832.4</v>
+      </c>
+      <c r="I70" t="n">
+        <v>810.2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>340.3</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-10-26 11:45</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:45</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>342.25</v>
+      </c>
+      <c r="H71" t="n">
+        <v>342.25</v>
+      </c>
+      <c r="I71" t="n">
+        <v>333.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1227</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:45</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1240.7</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1240.7</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1227</v>
       </c>
     </row>
   </sheetData>

--- a/data/entry_sl_signals.xlsx
+++ b/data/entry_sl_signals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,7 +779,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -795,17 +795,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-27 11:45</t>
+          <t>2026-10-30 11:00</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>688.1</v>
+        <v>687.65</v>
       </c>
       <c r="H10" t="n">
-        <v>688.1</v>
+        <v>687.65</v>
       </c>
       <c r="I10" t="n">
-        <v>683.85</v>
+        <v>669.5</v>
       </c>
     </row>
     <row r="11">
@@ -890,7 +890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -906,14 +906,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-28 09:45</t>
+          <t>2026-10-30 10:15</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>74.06999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>74.06999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>73.19</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-29 10:15</t>
+          <t>2026-10-30 12:00</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1183.6</v>
+        <v>1181.8</v>
       </c>
       <c r="H18" t="n">
-        <v>1183.6</v>
+        <v>1181.8</v>
       </c>
       <c r="I18" t="n">
         <v>1139.2</v>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>290.65</v>
+        <v>287.21</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>289.5</v>
+        <v>286.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-28 15:00</t>
+          <t>2026-10-28 10:45</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>291</v>
+        <v>289.8</v>
       </c>
       <c r="H23" t="n">
-        <v>291</v>
+        <v>289.8</v>
       </c>
       <c r="I23" t="n">
         <v>283.7</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1498,14 +1498,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-28 14:15</t>
+          <t>2026-10-30 14:00</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1137.8</v>
+        <v>1135.2</v>
       </c>
       <c r="H29" t="n">
-        <v>1137.8</v>
+        <v>1135.2</v>
       </c>
       <c r="I29" t="n">
         <v>1118.1</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1794,14 +1794,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-28 09:45</t>
+          <t>2026-10-30 10:15</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>74.06999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>74.06999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I37" t="n">
         <v>73.19</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1905,14 +1905,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-28 14:15</t>
+          <t>2026-10-30 14:00</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1137.8</v>
+        <v>1135.2</v>
       </c>
       <c r="H40" t="n">
-        <v>1137.8</v>
+        <v>1135.2</v>
       </c>
       <c r="I40" t="n">
         <v>1118.1</v>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2201,14 +2201,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-29 09:45</t>
+          <t>2026-10-30 10:15</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>512.9</v>
+        <v>511.8</v>
       </c>
       <c r="H48" t="n">
-        <v>512.9</v>
+        <v>511.8</v>
       </c>
       <c r="I48" t="n">
         <v>508.4</v>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -2312,17 +2312,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-28 14:30</t>
+          <t>2026-10-30 15:15</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1582.2</v>
+        <v>1580.8</v>
       </c>
       <c r="H51" t="n">
-        <v>1582.2</v>
+        <v>1580.8</v>
       </c>
       <c r="I51" t="n">
-        <v>1556.1</v>
+        <v>1553.3</v>
       </c>
     </row>
     <row r="52">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -2349,14 +2349,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-28 09:45</t>
+          <t>2026-10-30 10:15</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>74.06999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>74.06999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I52" t="n">
         <v>73.19</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2460,14 +2460,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-29 10:15</t>
+          <t>2026-10-30 12:00</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1183.6</v>
+        <v>1181.8</v>
       </c>
       <c r="H55" t="n">
-        <v>1183.6</v>
+        <v>1181.8</v>
       </c>
       <c r="I55" t="n">
         <v>1139.2</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -2719,14 +2719,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-28 14:15</t>
+          <t>2026-10-30 14:00</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1137.8</v>
+        <v>1135.2</v>
       </c>
       <c r="H62" t="n">
-        <v>1137.8</v>
+        <v>1135.2</v>
       </c>
       <c r="I62" t="n">
         <v>1118.1</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2830,14 +2830,14 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-29 09:45</t>
+          <t>2026-10-30 10:15</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>512.9</v>
+        <v>511.8</v>
       </c>
       <c r="H65" t="n">
-        <v>512.9</v>
+        <v>511.8</v>
       </c>
       <c r="I65" t="n">
         <v>508.4</v>
@@ -2929,26 +2929,26 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>290.65</v>
+        <v>287.21</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>289.5</v>
+        <v>286.6</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-28 15:00</t>
+          <t>2026-10-28 10:45</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>291</v>
+        <v>289.8</v>
       </c>
       <c r="H68" t="n">
-        <v>291</v>
+        <v>289.8</v>
       </c>
       <c r="I68" t="n">
         <v>283.7</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2978,17 +2978,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-30 15:15</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1169</v>
+        <v>1164.9</v>
       </c>
       <c r="H69" t="n">
-        <v>1169</v>
+        <v>1164.9</v>
       </c>
       <c r="I69" t="n">
-        <v>1156.2</v>
+        <v>1152.6</v>
       </c>
     </row>
     <row r="70">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -3015,14 +3015,14 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-30 14:00</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>832.4</v>
+        <v>827.8</v>
       </c>
       <c r="H70" t="n">
-        <v>832.4</v>
+        <v>827.8</v>
       </c>
       <c r="I70" t="n">
         <v>810.2</v>
@@ -3100,6 +3100,228 @@
       </c>
       <c r="I72" t="n">
         <v>1227</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>686.85</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-10-26 11:30</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>686.1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:00</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>687.65</v>
+      </c>
+      <c r="H73" t="n">
+        <v>687.65</v>
+      </c>
+      <c r="I73" t="n">
+        <v>669.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>510.4</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:15</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>511.8</v>
+      </c>
+      <c r="H74" t="n">
+        <v>511.8</v>
+      </c>
+      <c r="I74" t="n">
+        <v>508.4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1578.4</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:15</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1580.8</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1580.8</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1553.3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1177.6</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1169.8</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:00</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1181.8</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1181.8</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1139.2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1450.5</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:45</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1447</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:00</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1452.8</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1452.8</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1342.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1163.1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:15</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1162</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:15</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1164.9</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1164.9</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1152.6</v>
       </c>
     </row>
   </sheetData>
